--- a/research/traditional_assets/database/data/brazil/brazil_drugs_biotechnology.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_drugs_biotechnology.xlsx
@@ -1412,7 +1412,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1549,22 +1549,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.133964437723072</v>
+        <v>0.1335386586348135</v>
       </c>
       <c r="C2">
-        <v>452.6844161580559</v>
+        <v>450.0757671884803</v>
       </c>
       <c r="D2">
-        <v>448.8844161580558</v>
+        <v>451.0627671884803</v>
       </c>
       <c r="E2">
-        <v>-100.9</v>
+        <v>-96.113</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4.787000000000001</v>
       </c>
       <c r="G2">
         <v>3.8</v>
@@ -1585,28 +1585,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2407861</v>
       </c>
       <c r="N2">
-        <v>54.96666666666666</v>
+        <v>54.72588056666666</v>
       </c>
       <c r="O2">
-        <v>18.68866666666667</v>
+        <v>18.60679939266667</v>
       </c>
       <c r="P2">
-        <v>36.27799999999999</v>
+        <v>36.11908117399999</v>
       </c>
       <c r="Q2">
-        <v>42.97799999999999</v>
+        <v>42.819081174</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.133964437723072</v>
+        <v>0.1345522006412257</v>
       </c>
       <c r="T2">
-        <v>1.149078177305102</v>
+        <v>1.156738698487136</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>228.2800654467457</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1631,22 +1631,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1335386586348135</v>
+        <v>0.133112879546555</v>
       </c>
       <c r="C3">
-        <v>450.0757671884803</v>
+        <v>447.4883635682841</v>
       </c>
       <c r="D3">
-        <v>451.0627671884803</v>
+        <v>453.2623635682841</v>
       </c>
       <c r="E3">
-        <v>-96.113</v>
+        <v>-91.32600000000001</v>
       </c>
       <c r="F3">
-        <v>4.787000000000001</v>
+        <v>9.574000000000002</v>
       </c>
       <c r="G3">
         <v>3.8</v>
@@ -1667,28 +1667,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M3">
-        <v>0.2407861</v>
+        <v>0.4815722000000001</v>
       </c>
       <c r="N3">
-        <v>54.72588056666666</v>
+        <v>54.48509446666666</v>
       </c>
       <c r="O3">
-        <v>18.60679939266667</v>
+        <v>18.52493211866667</v>
       </c>
       <c r="P3">
-        <v>36.11908117399999</v>
+        <v>35.960162348</v>
       </c>
       <c r="Q3">
-        <v>42.819081174</v>
+        <v>42.660162348</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1345522006412257</v>
+        <v>0.1351519587209745</v>
       </c>
       <c r="T3">
-        <v>1.156738698487136</v>
+        <v>1.164555556836151</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>228.2800654467457</v>
+        <v>114.1400327233728</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1713,22 +1713,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.133112879546555</v>
+        <v>0.1326871004582966</v>
       </c>
       <c r="C4">
-        <v>447.4883635682841</v>
+        <v>444.9225176277937</v>
       </c>
       <c r="D4">
-        <v>453.2623635682841</v>
+        <v>455.4835176277937</v>
       </c>
       <c r="E4">
-        <v>-91.32600000000001</v>
+        <v>-86.539</v>
       </c>
       <c r="F4">
-        <v>9.574000000000002</v>
+        <v>14.361</v>
       </c>
       <c r="G4">
         <v>3.8</v>
@@ -1749,28 +1749,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M4">
-        <v>0.4815722000000001</v>
+        <v>0.7223583</v>
       </c>
       <c r="N4">
-        <v>54.48509446666666</v>
+        <v>54.24430836666666</v>
       </c>
       <c r="O4">
-        <v>18.52493211866667</v>
+        <v>18.44306484466667</v>
       </c>
       <c r="P4">
-        <v>35.960162348</v>
+        <v>35.80124352199999</v>
       </c>
       <c r="Q4">
-        <v>42.660162348</v>
+        <v>42.501243522</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1351519587209745</v>
+        <v>0.1357640829466976</v>
       </c>
       <c r="T4">
-        <v>1.164555556836151</v>
+        <v>1.172533587522258</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>114.1400327233728</v>
+        <v>76.09335514891524</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1326871004582966</v>
+        <v>0.1322613213700382</v>
       </c>
       <c r="C5">
-        <v>444.9225176277937</v>
+        <v>442.3785478496232</v>
       </c>
       <c r="D5">
-        <v>455.4835176277937</v>
+        <v>457.7265478496232</v>
       </c>
       <c r="E5">
-        <v>-86.539</v>
+        <v>-81.75200000000001</v>
       </c>
       <c r="F5">
-        <v>14.361</v>
+        <v>19.148</v>
       </c>
       <c r="G5">
         <v>3.8</v>
@@ -1831,28 +1831,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M5">
-        <v>0.7223583</v>
+        <v>0.9631444000000001</v>
       </c>
       <c r="N5">
-        <v>54.24430836666666</v>
+        <v>54.00352226666666</v>
       </c>
       <c r="O5">
-        <v>18.44306484466667</v>
+        <v>18.36119757066667</v>
       </c>
       <c r="P5">
-        <v>35.80124352199999</v>
+        <v>35.642324696</v>
       </c>
       <c r="Q5">
-        <v>42.501243522</v>
+        <v>42.342324696</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1357640829466976</v>
+        <v>0.1363889597604564</v>
       </c>
       <c r="T5">
-        <v>1.172533587522258</v>
+        <v>1.180677827180993</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>76.09335514891524</v>
+        <v>57.07001636168643</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1877,22 +1877,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1322613213700382</v>
+        <v>0.1318355422817797</v>
       </c>
       <c r="C6">
-        <v>442.3785478496232</v>
+        <v>439.8567790209084</v>
       </c>
       <c r="D6">
-        <v>457.7265478496232</v>
+        <v>459.9917790209084</v>
       </c>
       <c r="E6">
-        <v>-81.75200000000001</v>
+        <v>-76.965</v>
       </c>
       <c r="F6">
-        <v>19.148</v>
+        <v>23.935</v>
       </c>
       <c r="G6">
         <v>3.8</v>
@@ -1913,28 +1913,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M6">
-        <v>0.9631444000000001</v>
+        <v>1.2039305</v>
       </c>
       <c r="N6">
-        <v>54.00352226666666</v>
+        <v>53.76273616666666</v>
       </c>
       <c r="O6">
-        <v>18.36119757066667</v>
+        <v>18.27933029666667</v>
       </c>
       <c r="P6">
-        <v>35.642324696</v>
+        <v>35.48340587</v>
       </c>
       <c r="Q6">
-        <v>42.342324696</v>
+        <v>42.18340587</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1363889597604564</v>
+        <v>0.1370269918755576</v>
       </c>
       <c r="T6">
-        <v>1.180677827180993</v>
+        <v>1.188993524516753</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>57.07001636168643</v>
+        <v>45.65601308934914</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1959,22 +1959,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1318355422817797</v>
+        <v>0.1314097631935213</v>
       </c>
       <c r="C7">
-        <v>439.8567790209084</v>
+        <v>437.3575423900836</v>
       </c>
       <c r="D7">
-        <v>459.9917790209084</v>
+        <v>462.2795423900836</v>
       </c>
       <c r="E7">
-        <v>-76.965</v>
+        <v>-72.178</v>
       </c>
       <c r="F7">
-        <v>23.935</v>
+        <v>28.722</v>
       </c>
       <c r="G7">
         <v>3.8</v>
@@ -1995,28 +1995,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M7">
-        <v>1.2039305</v>
+        <v>1.4447166</v>
       </c>
       <c r="N7">
-        <v>53.76273616666666</v>
+        <v>53.52195006666666</v>
       </c>
       <c r="O7">
-        <v>18.27933029666667</v>
+        <v>18.19746302266667</v>
       </c>
       <c r="P7">
-        <v>35.48340587</v>
+        <v>35.32448704399999</v>
       </c>
       <c r="Q7">
-        <v>42.18340587</v>
+        <v>42.024487044</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1370269918755576</v>
+        <v>0.1376785991420439</v>
       </c>
       <c r="T7">
-        <v>1.188993524516753</v>
+        <v>1.197486151583062</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>45.65601308934914</v>
+        <v>38.04667757445762</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2041,22 +2041,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1314097631935213</v>
+        <v>0.1309839841052629</v>
       </c>
       <c r="C8">
-        <v>437.3575423900836</v>
+        <v>434.8811758283616</v>
       </c>
       <c r="D8">
-        <v>462.2795423900836</v>
+        <v>464.5901758283616</v>
       </c>
       <c r="E8">
-        <v>-72.178</v>
+        <v>-67.39100000000001</v>
       </c>
       <c r="F8">
-        <v>28.722</v>
+        <v>33.509</v>
       </c>
       <c r="G8">
         <v>3.8</v>
@@ -2077,28 +2077,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M8">
-        <v>1.4447166</v>
+        <v>1.6855027</v>
       </c>
       <c r="N8">
-        <v>53.52195006666666</v>
+        <v>53.28116396666666</v>
       </c>
       <c r="O8">
-        <v>18.19746302266667</v>
+        <v>18.11559574866667</v>
       </c>
       <c r="P8">
-        <v>35.32448704399999</v>
+        <v>35.16556821799999</v>
       </c>
       <c r="Q8">
-        <v>42.024487044</v>
+        <v>41.86556821799999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1376785991420439</v>
+        <v>0.1383442194680246</v>
       </c>
       <c r="T8">
-        <v>1.197486151583062</v>
+        <v>1.206161415790581</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>38.04667757445762</v>
+        <v>32.61143792096367</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2123,22 +2123,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1309839841052628</v>
+        <v>0.1305582050170044</v>
       </c>
       <c r="C9">
-        <v>434.8811758283618</v>
+        <v>432.4280239960801</v>
       </c>
       <c r="D9">
-        <v>464.5901758283618</v>
+        <v>466.9240239960801</v>
       </c>
       <c r="E9">
-        <v>-67.39099999999999</v>
+        <v>-62.604</v>
       </c>
       <c r="F9">
-        <v>33.50900000000001</v>
+        <v>38.29600000000001</v>
       </c>
       <c r="G9">
         <v>3.8</v>
@@ -2159,28 +2159,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M9">
-        <v>1.6855027</v>
+        <v>1.9262888</v>
       </c>
       <c r="N9">
-        <v>53.28116396666666</v>
+        <v>53.04037786666666</v>
       </c>
       <c r="O9">
-        <v>18.11559574866667</v>
+        <v>18.03372847466667</v>
       </c>
       <c r="P9">
-        <v>35.16556821799999</v>
+        <v>35.00664939199999</v>
       </c>
       <c r="Q9">
-        <v>41.86556821799999</v>
+        <v>41.706649392</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1383442194680246</v>
+        <v>0.1390243098010917</v>
       </c>
       <c r="T9">
-        <v>1.206161415790582</v>
+        <v>1.215025272698264</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>32.61143792096367</v>
+        <v>28.53500818084321</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2205,22 +2205,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1305582050170044</v>
+        <v>0.1301324259287459</v>
       </c>
       <c r="C10">
-        <v>432.4280239960801</v>
+        <v>429.9984385140852</v>
       </c>
       <c r="D10">
-        <v>466.9240239960801</v>
+        <v>469.2814385140852</v>
       </c>
       <c r="E10">
-        <v>-62.604</v>
+        <v>-57.817</v>
       </c>
       <c r="F10">
-        <v>38.29600000000001</v>
+        <v>43.08300000000001</v>
       </c>
       <c r="G10">
         <v>3.8</v>
@@ -2241,28 +2241,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M10">
-        <v>1.9262888</v>
+        <v>2.1670749</v>
       </c>
       <c r="N10">
-        <v>53.04037786666666</v>
+        <v>52.79959176666666</v>
       </c>
       <c r="O10">
-        <v>18.03372847466667</v>
+        <v>17.95186120066667</v>
       </c>
       <c r="P10">
-        <v>35.00664939199999</v>
+        <v>34.847730566</v>
       </c>
       <c r="Q10">
-        <v>41.706649392</v>
+        <v>41.547730566</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1390243098010917</v>
+        <v>0.1397193471744461</v>
       </c>
       <c r="T10">
-        <v>1.215025272698264</v>
+        <v>1.224083939647875</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>28.53500818084321</v>
+        <v>25.36445171630508</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2287,22 +2287,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1301324259287459</v>
+        <v>0.1297066468404875</v>
       </c>
       <c r="C11">
-        <v>429.9984385140852</v>
+        <v>427.5927781403365</v>
       </c>
       <c r="D11">
-        <v>469.2814385140852</v>
+        <v>471.6627781403365</v>
       </c>
       <c r="E11">
-        <v>-57.817</v>
+        <v>-53.03000000000001</v>
       </c>
       <c r="F11">
-        <v>43.08300000000001</v>
+        <v>47.87</v>
       </c>
       <c r="G11">
         <v>3.8</v>
@@ -2323,28 +2323,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M11">
-        <v>2.1670749</v>
+        <v>2.407861</v>
       </c>
       <c r="N11">
-        <v>52.79959176666666</v>
+        <v>52.55880566666666</v>
       </c>
       <c r="O11">
-        <v>17.95186120066667</v>
+        <v>17.86999392666667</v>
       </c>
       <c r="P11">
-        <v>34.847730566</v>
+        <v>34.68881174</v>
       </c>
       <c r="Q11">
-        <v>41.547730566</v>
+        <v>41.38881174</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1397193471744461</v>
+        <v>0.1404298298227639</v>
       </c>
       <c r="T11">
-        <v>1.224083939647875</v>
+        <v>1.233343910307476</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2361,7 +2361,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>25.36445171630508</v>
+        <v>22.82800654467458</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2369,22 +2369,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1297066468404875</v>
+        <v>0.1292808677522291</v>
       </c>
       <c r="C12">
-        <v>427.5927781403365</v>
+        <v>425.2114089519147</v>
       </c>
       <c r="D12">
-        <v>471.6627781403365</v>
+        <v>474.0684089519147</v>
       </c>
       <c r="E12">
-        <v>-53.03</v>
+        <v>-48.243</v>
       </c>
       <c r="F12">
-        <v>47.87</v>
+        <v>52.657</v>
       </c>
       <c r="G12">
         <v>3.8</v>
@@ -2405,28 +2405,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M12">
-        <v>2.407861</v>
+        <v>2.6486471</v>
       </c>
       <c r="N12">
-        <v>52.55880566666666</v>
+        <v>52.31801956666666</v>
       </c>
       <c r="O12">
-        <v>17.86999392666667</v>
+        <v>17.78812665266667</v>
       </c>
       <c r="P12">
-        <v>34.68881174</v>
+        <v>34.529892914</v>
       </c>
       <c r="Q12">
-        <v>41.38881174</v>
+        <v>41.229892914</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1404298298227639</v>
+        <v>0.1411562783732911</v>
       </c>
       <c r="T12">
-        <v>1.233343910307476</v>
+        <v>1.242811970195383</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>22.82800654467457</v>
+        <v>20.75273322243143</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2451,22 +2451,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1292808677522291</v>
+        <v>0.1288550886639706</v>
       </c>
       <c r="C13">
-        <v>425.2114089519147</v>
+        <v>422.8547045326263</v>
       </c>
       <c r="D13">
-        <v>474.0684089519147</v>
+        <v>476.4987045326263</v>
       </c>
       <c r="E13">
-        <v>-48.243</v>
+        <v>-43.456</v>
       </c>
       <c r="F13">
-        <v>52.657</v>
+        <v>57.444</v>
       </c>
       <c r="G13">
         <v>3.8</v>
@@ -2487,28 +2487,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M13">
-        <v>2.6486471</v>
+        <v>2.8894332</v>
       </c>
       <c r="N13">
-        <v>52.31801956666666</v>
+        <v>52.07723346666666</v>
       </c>
       <c r="O13">
-        <v>17.78812665266667</v>
+        <v>17.70625937866667</v>
       </c>
       <c r="P13">
-        <v>34.529892914</v>
+        <v>34.370974088</v>
       </c>
       <c r="Q13">
-        <v>41.229892914</v>
+        <v>41.070974088</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1411562783732911</v>
+        <v>0.1418992371181484</v>
       </c>
       <c r="T13">
-        <v>1.242811970195383</v>
+        <v>1.252495213262562</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.75273322243143</v>
+        <v>19.02333878722881</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2533,22 +2533,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1288550886639706</v>
+        <v>0.1284293095757122</v>
       </c>
       <c r="C14">
-        <v>422.8547045326263</v>
+        <v>420.5230461664125</v>
       </c>
       <c r="D14">
-        <v>476.4987045326263</v>
+        <v>478.9540461664125</v>
       </c>
       <c r="E14">
-        <v>-43.456</v>
+        <v>-38.669</v>
       </c>
       <c r="F14">
-        <v>57.444</v>
+        <v>62.23100000000001</v>
       </c>
       <c r="G14">
         <v>3.8</v>
@@ -2569,28 +2569,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M14">
-        <v>2.8894332</v>
+        <v>3.1302193</v>
       </c>
       <c r="N14">
-        <v>52.07723346666666</v>
+        <v>51.83644736666666</v>
       </c>
       <c r="O14">
-        <v>17.70625937866667</v>
+        <v>17.62439210466666</v>
       </c>
       <c r="P14">
-        <v>34.370974088</v>
+        <v>34.21205526199999</v>
       </c>
       <c r="Q14">
-        <v>41.070974088</v>
+        <v>40.912055262</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1418992371181484</v>
+        <v>0.1426592753743818</v>
       </c>
       <c r="T14">
-        <v>1.252495213262562</v>
+        <v>1.26240105961864</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>19.02333878722881</v>
+        <v>17.56000503436506</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2615,22 +2615,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1284293095757122</v>
+        <v>0.1280035304874537</v>
       </c>
       <c r="C15">
-        <v>420.5230461664125</v>
+        <v>418.2168230367629</v>
       </c>
       <c r="D15">
-        <v>478.9540461664125</v>
+        <v>481.4348230367629</v>
       </c>
       <c r="E15">
-        <v>-38.669</v>
+        <v>-33.88199999999999</v>
       </c>
       <c r="F15">
-        <v>62.23100000000001</v>
+        <v>67.01800000000001</v>
       </c>
       <c r="G15">
         <v>3.8</v>
@@ -2651,28 +2651,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M15">
-        <v>3.1302193</v>
+        <v>3.3710054</v>
       </c>
       <c r="N15">
-        <v>51.83644736666666</v>
+        <v>51.59566126666666</v>
       </c>
       <c r="O15">
-        <v>17.62439210466666</v>
+        <v>17.54252483066666</v>
       </c>
       <c r="P15">
-        <v>34.21205526199999</v>
+        <v>34.053136436</v>
       </c>
       <c r="Q15">
-        <v>40.912055262</v>
+        <v>40.753136436</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1426592753743818</v>
+        <v>0.1434369889388997</v>
       </c>
       <c r="T15">
-        <v>1.26240105961864</v>
+        <v>1.272537274494627</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2689,7 +2689,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.56000503436506</v>
+        <v>16.30571896048183</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2697,22 +2697,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1280035304874537</v>
+        <v>0.1275777513991953</v>
       </c>
       <c r="C16">
-        <v>418.2168230367629</v>
+        <v>415.9364324323654</v>
       </c>
       <c r="D16">
-        <v>481.4348230367629</v>
+        <v>483.9414324323654</v>
       </c>
       <c r="E16">
-        <v>-33.88199999999999</v>
+        <v>-29.09499999999998</v>
       </c>
       <c r="F16">
-        <v>67.01800000000001</v>
+        <v>71.80500000000002</v>
       </c>
       <c r="G16">
         <v>3.8</v>
@@ -2733,28 +2733,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M16">
-        <v>3.3710054</v>
+        <v>3.611791500000001</v>
       </c>
       <c r="N16">
-        <v>51.59566126666666</v>
+        <v>51.35487516666666</v>
       </c>
       <c r="O16">
-        <v>17.54252483066666</v>
+        <v>17.46065755666666</v>
       </c>
       <c r="P16">
-        <v>34.053136436</v>
+        <v>33.89421761</v>
       </c>
       <c r="Q16">
-        <v>40.753136436</v>
+        <v>40.59421761</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1434369889388997</v>
+        <v>0.1442330016461121</v>
       </c>
       <c r="T16">
-        <v>1.272537274494627</v>
+        <v>1.282911988544167</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.30571896048183</v>
+        <v>15.21867102978305</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2779,22 +2779,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1275777513991953</v>
+        <v>0.1271519723109368</v>
       </c>
       <c r="C17">
-        <v>415.9364324323654</v>
+        <v>413.6822799592081</v>
       </c>
       <c r="D17">
-        <v>483.9414324323654</v>
+        <v>486.4742799592082</v>
       </c>
       <c r="E17">
-        <v>-29.095</v>
+        <v>-24.30799999999999</v>
       </c>
       <c r="F17">
-        <v>71.80500000000001</v>
+        <v>76.59200000000001</v>
       </c>
       <c r="G17">
         <v>3.8</v>
@@ -2815,28 +2815,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M17">
-        <v>3.6117915</v>
+        <v>3.8525776</v>
       </c>
       <c r="N17">
-        <v>51.35487516666666</v>
+        <v>51.11408906666666</v>
       </c>
       <c r="O17">
-        <v>17.46065755666666</v>
+        <v>17.37879028266666</v>
       </c>
       <c r="P17">
-        <v>33.89421761</v>
+        <v>33.73529878399999</v>
       </c>
       <c r="Q17">
-        <v>40.59421761</v>
+        <v>40.435298784</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1442330016461121</v>
+        <v>0.1450479670368296</v>
       </c>
       <c r="T17">
-        <v>1.282911988544167</v>
+        <v>1.293533719594886</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.21867102978305</v>
+        <v>14.26750409042161</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1271519723109368</v>
+        <v>0.1267261932226784</v>
       </c>
       <c r="C18">
-        <v>413.6822799592081</v>
+        <v>411.4547797593812</v>
       </c>
       <c r="D18">
-        <v>486.4742799592082</v>
+        <v>489.0337797593812</v>
       </c>
       <c r="E18">
-        <v>-24.30799999999999</v>
+        <v>-19.52099999999999</v>
       </c>
       <c r="F18">
-        <v>76.59200000000001</v>
+        <v>81.37900000000002</v>
       </c>
       <c r="G18">
         <v>3.8</v>
@@ -2897,28 +2897,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M18">
-        <v>3.8525776</v>
+        <v>4.093363700000001</v>
       </c>
       <c r="N18">
-        <v>51.11408906666666</v>
+        <v>50.87330296666666</v>
       </c>
       <c r="O18">
-        <v>17.37879028266666</v>
+        <v>17.29692300866666</v>
       </c>
       <c r="P18">
-        <v>33.73529878399999</v>
+        <v>33.57637995799999</v>
       </c>
       <c r="Q18">
-        <v>40.435298784</v>
+        <v>40.27637995799999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1450479670368296</v>
+        <v>0.1458825701478053</v>
       </c>
       <c r="T18">
-        <v>1.293533719594886</v>
+        <v>1.304411395972129</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2935,7 +2935,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.26750409042161</v>
+        <v>13.42823914392621</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2943,22 +2943,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1267261932226784</v>
+        <v>0.1264786141344199</v>
       </c>
       <c r="C19">
-        <v>411.4547797593812</v>
+        <v>408.168481508158</v>
       </c>
       <c r="D19">
-        <v>489.0337797593812</v>
+        <v>490.5344815081581</v>
       </c>
       <c r="E19">
-        <v>-19.52099999999999</v>
+        <v>-14.73399999999998</v>
       </c>
       <c r="F19">
-        <v>81.37900000000002</v>
+        <v>86.16600000000003</v>
       </c>
       <c r="G19">
         <v>3.8</v>
@@ -2979,45 +2979,45 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M19">
-        <v>4.093363700000001</v>
+        <v>4.463398800000001</v>
       </c>
       <c r="N19">
-        <v>50.87330296666666</v>
+        <v>50.50326786666666</v>
       </c>
       <c r="O19">
-        <v>17.29692300866666</v>
+        <v>17.17111107466667</v>
       </c>
       <c r="P19">
-        <v>33.57637995799999</v>
+        <v>33.33215679199999</v>
       </c>
       <c r="Q19">
-        <v>40.27637995799999</v>
+        <v>40.03215679199999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1458825701478053</v>
+        <v>0.1467375294322194</v>
       </c>
       <c r="T19">
-        <v>1.304411395972129</v>
+        <v>1.315554381529305</v>
       </c>
       <c r="U19">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.34</v>
       </c>
       <c r="W19">
-        <v>0.03319799999999999</v>
+        <v>0.034188</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>13.42823914392621</v>
+        <v>12.31497993561916</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3025,22 +3025,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1264786141344199</v>
+        <v>0.1260627350461615</v>
       </c>
       <c r="C20">
-        <v>408.1684815081581</v>
+        <v>405.9231720300621</v>
       </c>
       <c r="D20">
-        <v>490.5344815081581</v>
+        <v>493.0761720300621</v>
       </c>
       <c r="E20">
-        <v>-14.73399999999999</v>
+        <v>-9.947000000000003</v>
       </c>
       <c r="F20">
-        <v>86.16600000000001</v>
+        <v>90.953</v>
       </c>
       <c r="G20">
         <v>3.8</v>
@@ -3061,28 +3061,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M20">
-        <v>4.4633988</v>
+        <v>4.7113654</v>
       </c>
       <c r="N20">
-        <v>50.50326786666666</v>
+        <v>50.25530126666666</v>
       </c>
       <c r="O20">
-        <v>17.17111107466667</v>
+        <v>17.08680243066667</v>
       </c>
       <c r="P20">
-        <v>33.33215679199999</v>
+        <v>33.168498836</v>
       </c>
       <c r="Q20">
-        <v>40.03215679199999</v>
+        <v>39.868498836</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1467375294322194</v>
+        <v>0.1476135988224216</v>
       </c>
       <c r="T20">
-        <v>1.315554381529305</v>
+        <v>1.326972502532336</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>12.31497993561917</v>
+        <v>11.66682309690237</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3107,22 +3107,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1260627350461615</v>
+        <v>0.1256468559579031</v>
       </c>
       <c r="C21">
-        <v>405.9231720300621</v>
+        <v>403.7043391345244</v>
       </c>
       <c r="D21">
-        <v>493.0761720300621</v>
+        <v>495.6443391345244</v>
       </c>
       <c r="E21">
-        <v>-9.947000000000003</v>
+        <v>-5.159999999999997</v>
       </c>
       <c r="F21">
-        <v>90.953</v>
+        <v>95.74000000000001</v>
       </c>
       <c r="G21">
         <v>3.8</v>
@@ -3143,28 +3143,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M21">
-        <v>4.7113654</v>
+        <v>4.959332000000001</v>
       </c>
       <c r="N21">
-        <v>50.25530126666666</v>
+        <v>50.00733466666666</v>
       </c>
       <c r="O21">
-        <v>17.08680243066667</v>
+        <v>17.00249378666667</v>
       </c>
       <c r="P21">
-        <v>33.168498836</v>
+        <v>33.00484087999999</v>
       </c>
       <c r="Q21">
-        <v>39.868498836</v>
+        <v>39.70484087999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1476135988224216</v>
+        <v>0.1485115699473788</v>
       </c>
       <c r="T21">
-        <v>1.326972502532336</v>
+        <v>1.338676076560444</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.66682309690237</v>
+        <v>11.08348194205725</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3189,22 +3189,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1256468559579031</v>
+        <v>0.1252309768696446</v>
       </c>
       <c r="C22">
-        <v>403.7043391345244</v>
+        <v>401.5123986941974</v>
       </c>
       <c r="D22">
-        <v>495.6443391345244</v>
+        <v>498.2393986941973</v>
       </c>
       <c r="E22">
-        <v>-5.159999999999997</v>
+        <v>-0.3729999999999905</v>
       </c>
       <c r="F22">
-        <v>95.74000000000001</v>
+        <v>100.527</v>
       </c>
       <c r="G22">
         <v>3.8</v>
@@ -3225,28 +3225,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M22">
-        <v>4.959332000000001</v>
+        <v>5.207298600000001</v>
       </c>
       <c r="N22">
-        <v>50.00733466666666</v>
+        <v>49.75936806666666</v>
       </c>
       <c r="O22">
-        <v>17.00249378666667</v>
+        <v>16.91818514266667</v>
       </c>
       <c r="P22">
-        <v>33.00484087999999</v>
+        <v>32.84118292399999</v>
       </c>
       <c r="Q22">
-        <v>39.70484087999999</v>
+        <v>39.541182924</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1485115699473788</v>
+        <v>0.1494322745185375</v>
       </c>
       <c r="T22">
-        <v>1.338676076560444</v>
+        <v>1.350675943601922</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3263,7 +3263,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.08348194205725</v>
+        <v>10.55569708767357</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3271,22 +3271,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1252309768696446</v>
+        <v>0.1248150977813862</v>
       </c>
       <c r="C23">
-        <v>401.5123986941974</v>
+        <v>399.3477753371607</v>
       </c>
       <c r="D23">
-        <v>498.2393986941973</v>
+        <v>500.8617753371607</v>
       </c>
       <c r="E23">
-        <v>-0.3730000000000047</v>
+        <v>4.414000000000001</v>
       </c>
       <c r="F23">
-        <v>100.527</v>
+        <v>105.314</v>
       </c>
       <c r="G23">
         <v>3.8</v>
@@ -3307,28 +3307,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M23">
-        <v>5.2072986</v>
+        <v>5.4552652</v>
       </c>
       <c r="N23">
-        <v>49.75936806666666</v>
+        <v>49.51140146666666</v>
       </c>
       <c r="O23">
-        <v>16.91818514266667</v>
+        <v>16.83387649866667</v>
       </c>
       <c r="P23">
-        <v>32.84118292399999</v>
+        <v>32.677524968</v>
       </c>
       <c r="Q23">
-        <v>39.541182924</v>
+        <v>39.377524968</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1494322745185375</v>
+        <v>0.150376586899213</v>
       </c>
       <c r="T23">
-        <v>1.350675943601921</v>
+        <v>1.362983499541898</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3345,7 +3345,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.55569708767357</v>
+        <v>10.0758926745975</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3353,22 +3353,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1248150977813862</v>
+        <v>0.1246572786931277</v>
       </c>
       <c r="C24">
-        <v>399.3477753371607</v>
+        <v>395.5631628153646</v>
       </c>
       <c r="D24">
-        <v>500.8617753371607</v>
+        <v>501.8641628153646</v>
       </c>
       <c r="E24">
-        <v>4.414000000000001</v>
+        <v>9.201000000000008</v>
       </c>
       <c r="F24">
-        <v>105.314</v>
+        <v>110.101</v>
       </c>
       <c r="G24">
         <v>3.8</v>
@@ -3389,45 +3389,45 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M24">
-        <v>5.4552652</v>
+        <v>5.890403500000001</v>
       </c>
       <c r="N24">
-        <v>49.51140146666666</v>
+        <v>49.07626316666666</v>
       </c>
       <c r="O24">
-        <v>16.83387649866667</v>
+        <v>16.68592947666667</v>
       </c>
       <c r="P24">
-        <v>32.677524968</v>
+        <v>32.39033369</v>
       </c>
       <c r="Q24">
-        <v>39.377524968</v>
+        <v>39.09033369</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.150376586899213</v>
+        <v>0.1513454268741918</v>
       </c>
       <c r="T24">
-        <v>1.362983499541898</v>
+        <v>1.375610732259537</v>
       </c>
       <c r="U24">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V24">
         <v>0.34</v>
       </c>
       <c r="W24">
-        <v>0.034188</v>
+        <v>0.03530999999999999</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>10.0758926745975</v>
+        <v>9.331562203958805</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3435,22 +3435,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1246572786931277</v>
+        <v>0.1242526196048693</v>
       </c>
       <c r="C25">
-        <v>395.5631628153646</v>
+        <v>393.3647812143078</v>
       </c>
       <c r="D25">
-        <v>501.8641628153646</v>
+        <v>504.4527812143078</v>
       </c>
       <c r="E25">
-        <v>9.201000000000008</v>
+        <v>13.98800000000001</v>
       </c>
       <c r="F25">
-        <v>110.101</v>
+        <v>114.888</v>
       </c>
       <c r="G25">
         <v>3.8</v>
@@ -3471,28 +3471,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M25">
-        <v>5.890403500000001</v>
+        <v>6.146508000000001</v>
       </c>
       <c r="N25">
-        <v>49.07626316666666</v>
+        <v>48.82015866666666</v>
       </c>
       <c r="O25">
-        <v>16.68592947666667</v>
+        <v>16.59885394666667</v>
       </c>
       <c r="P25">
-        <v>32.39033369</v>
+        <v>32.22130471999999</v>
       </c>
       <c r="Q25">
-        <v>39.09033369</v>
+        <v>38.92130471999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1513454268741918</v>
+        <v>0.1523397626379859</v>
       </c>
       <c r="T25">
-        <v>1.375610732259537</v>
+        <v>1.388570260575008</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3509,7 +3509,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.331562203958805</v>
+        <v>8.942747112127186</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3517,22 +3517,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1242526196048693</v>
+        <v>0.1238479605166108</v>
       </c>
       <c r="C26">
-        <v>393.3647812143078</v>
+        <v>391.1932422867616</v>
       </c>
       <c r="D26">
-        <v>504.4527812143078</v>
+        <v>507.0682422867616</v>
       </c>
       <c r="E26">
-        <v>13.988</v>
+        <v>18.77500000000001</v>
       </c>
       <c r="F26">
-        <v>114.888</v>
+        <v>119.675</v>
       </c>
       <c r="G26">
         <v>3.8</v>
@@ -3553,28 +3553,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M26">
-        <v>6.146508</v>
+        <v>6.4026125</v>
       </c>
       <c r="N26">
-        <v>48.82015866666666</v>
+        <v>48.56405416666666</v>
       </c>
       <c r="O26">
-        <v>16.59885394666667</v>
+        <v>16.51177841666667</v>
       </c>
       <c r="P26">
-        <v>32.22130471999999</v>
+        <v>32.05227574999999</v>
       </c>
       <c r="Q26">
-        <v>38.92130471999999</v>
+        <v>38.75227575</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1523397626379859</v>
+        <v>0.1533606140221478</v>
       </c>
       <c r="T26">
-        <v>1.388570260575008</v>
+        <v>1.401875376312225</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.94274711212719</v>
+        <v>8.585037227642101</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3599,22 +3599,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1238479605166108</v>
+        <v>0.1234433014283524</v>
       </c>
       <c r="C27">
-        <v>391.1932422867616</v>
+        <v>389.0489657263093</v>
       </c>
       <c r="D27">
-        <v>507.0682422867616</v>
+        <v>509.7109657263094</v>
       </c>
       <c r="E27">
-        <v>18.77500000000001</v>
+        <v>23.56200000000001</v>
       </c>
       <c r="F27">
-        <v>119.675</v>
+        <v>124.462</v>
       </c>
       <c r="G27">
         <v>3.8</v>
@@ -3635,28 +3635,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M27">
-        <v>6.4026125</v>
+        <v>6.658717000000001</v>
       </c>
       <c r="N27">
-        <v>48.56405416666666</v>
+        <v>48.30794966666666</v>
       </c>
       <c r="O27">
-        <v>16.51177841666667</v>
+        <v>16.42470288666667</v>
       </c>
       <c r="P27">
-        <v>32.05227574999999</v>
+        <v>31.88324677999999</v>
       </c>
       <c r="Q27">
-        <v>38.75227575</v>
+        <v>38.58324678</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1533606140221478</v>
+        <v>0.15440905598426</v>
       </c>
       <c r="T27">
-        <v>1.401875376312225</v>
+        <v>1.415540089772069</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.585037227642101</v>
+        <v>8.254843488117404</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3681,22 +3681,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1234433014283524</v>
+        <v>0.1230386423400939</v>
       </c>
       <c r="C28">
-        <v>389.0489657263093</v>
+        <v>386.9323800217594</v>
       </c>
       <c r="D28">
-        <v>509.7109657263094</v>
+        <v>512.3813800217595</v>
       </c>
       <c r="E28">
-        <v>23.56200000000001</v>
+        <v>28.34900000000002</v>
       </c>
       <c r="F28">
-        <v>124.462</v>
+        <v>129.249</v>
       </c>
       <c r="G28">
         <v>3.8</v>
@@ -3717,28 +3717,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M28">
-        <v>6.658717000000001</v>
+        <v>6.914821500000001</v>
       </c>
       <c r="N28">
-        <v>48.30794966666666</v>
+        <v>48.05184516666666</v>
       </c>
       <c r="O28">
-        <v>16.42470288666667</v>
+        <v>16.33762735666667</v>
       </c>
       <c r="P28">
-        <v>31.88324677999999</v>
+        <v>31.71421780999999</v>
       </c>
       <c r="Q28">
-        <v>38.58324678</v>
+        <v>38.41421781</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.15440905598426</v>
+        <v>0.1554862223836903</v>
       </c>
       <c r="T28">
-        <v>1.415540089772069</v>
+        <v>1.429579178943142</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3755,7 +3755,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.254843488117404</v>
+        <v>7.949108544113055</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3763,22 +3763,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1230386423400939</v>
+        <v>0.1226339832518355</v>
       </c>
       <c r="C29">
-        <v>386.9323800217594</v>
+        <v>384.8439226887537</v>
       </c>
       <c r="D29">
-        <v>512.3813800217595</v>
+        <v>515.0799226887538</v>
       </c>
       <c r="E29">
-        <v>28.34900000000002</v>
+        <v>33.13600000000002</v>
       </c>
       <c r="F29">
-        <v>129.249</v>
+        <v>134.036</v>
       </c>
       <c r="G29">
         <v>3.8</v>
@@ -3799,28 +3799,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M29">
-        <v>6.914821500000001</v>
+        <v>7.170926000000001</v>
       </c>
       <c r="N29">
-        <v>48.05184516666666</v>
+        <v>47.79574066666666</v>
       </c>
       <c r="O29">
-        <v>16.33762735666667</v>
+        <v>16.25055182666667</v>
       </c>
       <c r="P29">
-        <v>31.71421780999999</v>
+        <v>31.54518883999999</v>
       </c>
       <c r="Q29">
-        <v>38.41421781</v>
+        <v>38.24518884</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1554862223836903</v>
+        <v>0.1565933100719938</v>
       </c>
       <c r="T29">
-        <v>1.429579178943142</v>
+        <v>1.444008242813412</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3837,7 +3837,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.949108544113055</v>
+        <v>7.665211810394731</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3845,22 +3845,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1226339832518355</v>
+        <v>0.122382444163577</v>
       </c>
       <c r="C30">
-        <v>384.8439226887537</v>
+        <v>381.7487299371176</v>
       </c>
       <c r="D30">
-        <v>515.0799226887538</v>
+        <v>516.7717299371177</v>
       </c>
       <c r="E30">
-        <v>33.13600000000002</v>
+        <v>37.92300000000003</v>
       </c>
       <c r="F30">
-        <v>134.036</v>
+        <v>138.823</v>
       </c>
       <c r="G30">
         <v>3.8</v>
@@ -3881,45 +3881,45 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M30">
-        <v>7.170926000000001</v>
+        <v>7.538088900000002</v>
       </c>
       <c r="N30">
-        <v>47.79574066666666</v>
+        <v>47.42857776666666</v>
       </c>
       <c r="O30">
-        <v>16.25055182666667</v>
+        <v>16.12571644066667</v>
       </c>
       <c r="P30">
-        <v>31.54518883999999</v>
+        <v>31.302861326</v>
       </c>
       <c r="Q30">
-        <v>38.24518884</v>
+        <v>38.002861326</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1565933100719938</v>
+        <v>0.1577315833289818</v>
       </c>
       <c r="T30">
-        <v>1.444008242813412</v>
+        <v>1.458843759187069</v>
       </c>
       <c r="U30">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V30">
         <v>0.34</v>
       </c>
       <c r="W30">
-        <v>0.03530999999999999</v>
+        <v>0.03583799999999999</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y30">
-        <v>7.665211810394731</v>
+        <v>7.291857047038362</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.122382444163577</v>
+        <v>0.1219830650753186</v>
       </c>
       <c r="C31">
-        <v>381.7487299371177</v>
+        <v>379.6708336222474</v>
       </c>
       <c r="D31">
-        <v>516.7717299371177</v>
+        <v>519.4808336222475</v>
       </c>
       <c r="E31">
-        <v>37.923</v>
+        <v>42.71000000000001</v>
       </c>
       <c r="F31">
-        <v>138.823</v>
+        <v>143.61</v>
       </c>
       <c r="G31">
         <v>3.8</v>
@@ -3963,28 +3963,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M31">
-        <v>7.538088900000001</v>
+        <v>7.798023000000001</v>
       </c>
       <c r="N31">
-        <v>47.42857776666666</v>
+        <v>47.16864366666666</v>
       </c>
       <c r="O31">
-        <v>16.12571644066667</v>
+        <v>16.03733884666667</v>
       </c>
       <c r="P31">
-        <v>31.302861326</v>
+        <v>31.13130481999999</v>
       </c>
       <c r="Q31">
-        <v>38.002861326</v>
+        <v>37.83130482</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1577315833289818</v>
+        <v>0.1589023786790266</v>
       </c>
       <c r="T31">
-        <v>1.458843759187069</v>
+        <v>1.474103147457117</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -4001,7 +4001,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.291857047038363</v>
+        <v>7.048795145470417</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4009,22 +4009,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1219830650753186</v>
+        <v>0.1215836859870602</v>
       </c>
       <c r="C32">
-        <v>379.6708336222474</v>
+        <v>377.6214911932344</v>
       </c>
       <c r="D32">
-        <v>519.4808336222475</v>
+        <v>522.2184911932345</v>
       </c>
       <c r="E32">
-        <v>42.71000000000001</v>
+        <v>47.49700000000001</v>
       </c>
       <c r="F32">
-        <v>143.61</v>
+        <v>148.397</v>
       </c>
       <c r="G32">
         <v>3.8</v>
@@ -4045,28 +4045,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M32">
-        <v>7.798023000000001</v>
+        <v>8.057957100000001</v>
       </c>
       <c r="N32">
-        <v>47.16864366666666</v>
+        <v>46.90870956666666</v>
       </c>
       <c r="O32">
-        <v>16.03733884666667</v>
+        <v>15.94896125266667</v>
       </c>
       <c r="P32">
-        <v>31.13130481999999</v>
+        <v>30.959748314</v>
       </c>
       <c r="Q32">
-        <v>37.83130482</v>
+        <v>37.659748314</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1589023786790266</v>
+        <v>0.1601071101261742</v>
       </c>
       <c r="T32">
-        <v>1.474103147457117</v>
+        <v>1.489804836836441</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.048795145470417</v>
+        <v>6.821414656906854</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4091,22 +4091,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1215836859870602</v>
+        <v>0.1211843068988017</v>
       </c>
       <c r="C33">
-        <v>377.6214911932344</v>
+        <v>375.601156477621</v>
       </c>
       <c r="D33">
-        <v>522.2184911932345</v>
+        <v>524.9851564776211</v>
       </c>
       <c r="E33">
-        <v>47.49700000000001</v>
+        <v>52.28400000000002</v>
       </c>
       <c r="F33">
-        <v>148.397</v>
+        <v>153.184</v>
       </c>
       <c r="G33">
         <v>3.8</v>
@@ -4127,28 +4127,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M33">
-        <v>8.057957100000001</v>
+        <v>8.317891200000002</v>
       </c>
       <c r="N33">
-        <v>46.90870956666666</v>
+        <v>46.64877546666666</v>
       </c>
       <c r="O33">
-        <v>15.94896125266667</v>
+        <v>15.86058365866667</v>
       </c>
       <c r="P33">
-        <v>30.959748314</v>
+        <v>30.788191808</v>
       </c>
       <c r="Q33">
-        <v>37.659748314</v>
+        <v>37.488191808</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1601071101261742</v>
+        <v>0.161347274851179</v>
       </c>
       <c r="T33">
-        <v>1.489804836836441</v>
+        <v>1.505968340609275</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.821414656906854</v>
+        <v>6.608245448878515</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4173,22 +4173,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1211843068988017</v>
+        <v>0.1207849278105433</v>
       </c>
       <c r="C34">
-        <v>375.601156477621</v>
+        <v>373.6102929715177</v>
       </c>
       <c r="D34">
-        <v>524.9851564776211</v>
+        <v>527.7812929715177</v>
       </c>
       <c r="E34">
-        <v>52.28400000000002</v>
+        <v>57.07100000000003</v>
       </c>
       <c r="F34">
-        <v>153.184</v>
+        <v>157.971</v>
       </c>
       <c r="G34">
         <v>3.8</v>
@@ -4209,28 +4209,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M34">
-        <v>8.317891200000002</v>
+        <v>8.577825300000002</v>
       </c>
       <c r="N34">
-        <v>46.64877546666666</v>
+        <v>46.38884136666666</v>
       </c>
       <c r="O34">
-        <v>15.86058365866667</v>
+        <v>15.77220606466667</v>
       </c>
       <c r="P34">
-        <v>30.788191808</v>
+        <v>30.616635302</v>
       </c>
       <c r="Q34">
-        <v>37.488191808</v>
+        <v>37.31663530199999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.161347274851179</v>
+        <v>0.1626244594187213</v>
       </c>
       <c r="T34">
-        <v>1.505968340609275</v>
+        <v>1.522614337032044</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4247,7 +4247,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.608245448878515</v>
+        <v>6.407995586791287</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4255,22 +4255,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1207849278105433</v>
+        <v>0.1203855487222848</v>
       </c>
       <c r="C35">
-        <v>373.6102929715177</v>
+        <v>371.6493740984616</v>
       </c>
       <c r="D35">
-        <v>527.7812929715177</v>
+        <v>530.6073740984617</v>
       </c>
       <c r="E35">
-        <v>57.07100000000003</v>
+        <v>61.85800000000003</v>
       </c>
       <c r="F35">
-        <v>157.971</v>
+        <v>162.758</v>
       </c>
       <c r="G35">
         <v>3.8</v>
@@ -4291,28 +4291,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M35">
-        <v>8.577825300000002</v>
+        <v>8.837759400000003</v>
       </c>
       <c r="N35">
-        <v>46.38884136666666</v>
+        <v>46.12890726666666</v>
       </c>
       <c r="O35">
-        <v>15.77220606466667</v>
+        <v>15.68382847066666</v>
       </c>
       <c r="P35">
-        <v>30.616635302</v>
+        <v>30.44507879599999</v>
       </c>
       <c r="Q35">
-        <v>37.31663530199999</v>
+        <v>37.14507879599999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1626244594187213</v>
+        <v>0.1639403465489164</v>
       </c>
       <c r="T35">
-        <v>1.522614337032044</v>
+        <v>1.539764757588837</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4329,7 +4329,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.407995586791287</v>
+        <v>6.219525128356248</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4337,22 +4337,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1203855487222848</v>
+        <v>0.1202171696340264</v>
       </c>
       <c r="C36">
-        <v>371.6493740984616</v>
+        <v>368.0629463093277</v>
       </c>
       <c r="D36">
-        <v>530.6073740984617</v>
+        <v>531.8079463093278</v>
       </c>
       <c r="E36">
-        <v>61.85800000000003</v>
+        <v>66.64500000000004</v>
       </c>
       <c r="F36">
-        <v>162.758</v>
+        <v>167.545</v>
       </c>
       <c r="G36">
         <v>3.8</v>
@@ -4373,45 +4373,45 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M36">
-        <v>8.837759400000003</v>
+        <v>9.265238500000002</v>
       </c>
       <c r="N36">
-        <v>46.12890726666666</v>
+        <v>45.70142816666666</v>
       </c>
       <c r="O36">
-        <v>15.68382847066666</v>
+        <v>15.53848557666667</v>
       </c>
       <c r="P36">
-        <v>30.44507879599999</v>
+        <v>30.16294258999999</v>
       </c>
       <c r="Q36">
-        <v>37.14507879599999</v>
+        <v>36.86294259</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1639403465489164</v>
+        <v>0.1652967225138867</v>
       </c>
       <c r="T36">
-        <v>1.539764757588837</v>
+        <v>1.557442883393531</v>
       </c>
       <c r="U36">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V36">
         <v>0.34</v>
       </c>
       <c r="W36">
-        <v>0.03583799999999999</v>
+        <v>0.036498</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>6.219525128356248</v>
+        <v>5.932568996110207</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4419,22 +4419,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1202171696340264</v>
+        <v>0.1198243905457679</v>
       </c>
       <c r="C37">
-        <v>368.0629463093277</v>
+        <v>366.0977600215368</v>
       </c>
       <c r="D37">
-        <v>531.8079463093278</v>
+        <v>534.6297600215369</v>
       </c>
       <c r="E37">
-        <v>66.64500000000004</v>
+        <v>71.43200000000004</v>
       </c>
       <c r="F37">
-        <v>167.545</v>
+        <v>172.3320000000001</v>
       </c>
       <c r="G37">
         <v>3.8</v>
@@ -4455,28 +4455,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M37">
-        <v>9.265238500000002</v>
+        <v>9.529959600000003</v>
       </c>
       <c r="N37">
-        <v>45.70142816666666</v>
+        <v>45.43670706666666</v>
       </c>
       <c r="O37">
-        <v>15.53848557666667</v>
+        <v>15.44848040266666</v>
       </c>
       <c r="P37">
-        <v>30.16294258999999</v>
+        <v>29.98822666399999</v>
       </c>
       <c r="Q37">
-        <v>36.86294259</v>
+        <v>36.688226664</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1652967225138867</v>
+        <v>0.1666954852277624</v>
       </c>
       <c r="T37">
-        <v>1.557442883393531</v>
+        <v>1.575673450629621</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.932568996110207</v>
+        <v>5.767775412884924</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4501,22 +4501,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1198243905457679</v>
+        <v>0.1194316114575095</v>
       </c>
       <c r="C38">
-        <v>366.0977600215368</v>
+        <v>364.1626789941138</v>
       </c>
       <c r="D38">
-        <v>534.6297600215369</v>
+        <v>537.4816789941138</v>
       </c>
       <c r="E38">
-        <v>71.43200000000002</v>
+        <v>76.21900000000002</v>
       </c>
       <c r="F38">
-        <v>172.332</v>
+        <v>177.119</v>
       </c>
       <c r="G38">
         <v>3.8</v>
@@ -4537,28 +4537,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M38">
-        <v>9.529959600000002</v>
+        <v>9.794680700000002</v>
       </c>
       <c r="N38">
-        <v>45.43670706666666</v>
+        <v>45.17198596666666</v>
       </c>
       <c r="O38">
-        <v>15.44848040266666</v>
+        <v>15.35847522866667</v>
       </c>
       <c r="P38">
-        <v>29.98822666399999</v>
+        <v>29.81351073799999</v>
       </c>
       <c r="Q38">
-        <v>36.688226664</v>
+        <v>36.51351073799999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1666954852277624</v>
+        <v>0.1681386531071579</v>
       </c>
       <c r="T38">
-        <v>1.575673450629621</v>
+        <v>1.594482766031937</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.767775412884925</v>
+        <v>5.611889590915061</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4583,22 +4583,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1194316114575095</v>
+        <v>0.1190388323692511</v>
       </c>
       <c r="C39">
-        <v>364.1626789941138</v>
+        <v>362.2581875896435</v>
       </c>
       <c r="D39">
-        <v>537.4816789941138</v>
+        <v>540.3641875896435</v>
       </c>
       <c r="E39">
-        <v>76.21900000000002</v>
+        <v>81.006</v>
       </c>
       <c r="F39">
-        <v>177.119</v>
+        <v>181.906</v>
       </c>
       <c r="G39">
         <v>3.8</v>
@@ -4619,28 +4619,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M39">
-        <v>9.794680700000002</v>
+        <v>10.0594018</v>
       </c>
       <c r="N39">
-        <v>45.17198596666666</v>
+        <v>44.90726486666667</v>
       </c>
       <c r="O39">
-        <v>15.35847522866667</v>
+        <v>15.26847005466667</v>
       </c>
       <c r="P39">
-        <v>29.81351073799999</v>
+        <v>29.638794812</v>
       </c>
       <c r="Q39">
-        <v>36.51351073799999</v>
+        <v>36.338794812</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1681386531071579</v>
+        <v>0.1696283747891146</v>
       </c>
       <c r="T39">
-        <v>1.594482766031937</v>
+        <v>1.613898833544005</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.611889590915061</v>
+        <v>5.464208285890983</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4665,22 +4665,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1190388323692511</v>
+        <v>0.1186460532809926</v>
       </c>
       <c r="C40">
-        <v>362.2581875896435</v>
+        <v>360.3847806172614</v>
       </c>
       <c r="D40">
-        <v>540.3641875896435</v>
+        <v>543.2777806172614</v>
       </c>
       <c r="E40">
-        <v>81.006</v>
+        <v>85.79300000000001</v>
       </c>
       <c r="F40">
-        <v>181.906</v>
+        <v>186.693</v>
       </c>
       <c r="G40">
         <v>3.8</v>
@@ -4701,28 +4701,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M40">
-        <v>10.0594018</v>
+        <v>10.3241229</v>
       </c>
       <c r="N40">
-        <v>44.90726486666667</v>
+        <v>44.64254376666666</v>
       </c>
       <c r="O40">
-        <v>15.26847005466667</v>
+        <v>15.17846488066667</v>
       </c>
       <c r="P40">
-        <v>29.638794812</v>
+        <v>29.464078886</v>
       </c>
       <c r="Q40">
-        <v>36.338794812</v>
+        <v>36.164078886</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1696283747891146</v>
+        <v>0.1711669398049059</v>
       </c>
       <c r="T40">
-        <v>1.613898833544005</v>
+        <v>1.633951493433517</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4739,7 +4739,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.464208285890983</v>
+        <v>5.324100381124547</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4747,22 +4747,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1186460532809926</v>
+        <v>0.1182532741927342</v>
       </c>
       <c r="C41">
-        <v>360.3847806172614</v>
+        <v>358.5429636158138</v>
       </c>
       <c r="D41">
-        <v>543.2777806172614</v>
+        <v>546.2229636158139</v>
       </c>
       <c r="E41">
-        <v>85.79300000000001</v>
+        <v>90.58000000000001</v>
       </c>
       <c r="F41">
-        <v>186.693</v>
+        <v>191.48</v>
       </c>
       <c r="G41">
         <v>3.8</v>
@@ -4783,28 +4783,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M41">
-        <v>10.3241229</v>
+        <v>10.588844</v>
       </c>
       <c r="N41">
-        <v>44.64254376666666</v>
+        <v>44.37782266666666</v>
       </c>
       <c r="O41">
-        <v>15.17846488066667</v>
+        <v>15.08845970666667</v>
       </c>
       <c r="P41">
-        <v>29.464078886</v>
+        <v>29.28936295999999</v>
       </c>
       <c r="Q41">
-        <v>36.164078886</v>
+        <v>35.98936295999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1711669398049059</v>
+        <v>0.1727567903212236</v>
       </c>
       <c r="T41">
-        <v>1.633951493433517</v>
+        <v>1.654672575319347</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4821,7 +4821,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.324100381124547</v>
+        <v>5.190997871596433</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4829,22 +4829,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1182532741927342</v>
+        <v>0.1178604951044757</v>
       </c>
       <c r="C42">
-        <v>358.5429636158138</v>
+        <v>356.7332531462812</v>
       </c>
       <c r="D42">
-        <v>546.2229636158139</v>
+        <v>549.2002531462813</v>
       </c>
       <c r="E42">
-        <v>90.58000000000001</v>
+        <v>95.36700000000002</v>
       </c>
       <c r="F42">
-        <v>191.48</v>
+        <v>196.267</v>
       </c>
       <c r="G42">
         <v>3.8</v>
@@ -4865,28 +4865,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M42">
-        <v>10.588844</v>
+        <v>10.8535651</v>
       </c>
       <c r="N42">
-        <v>44.37782266666666</v>
+        <v>44.11310156666666</v>
       </c>
       <c r="O42">
-        <v>15.08845970666667</v>
+        <v>14.99845453266667</v>
       </c>
       <c r="P42">
-        <v>29.28936295999999</v>
+        <v>29.11464703399999</v>
       </c>
       <c r="Q42">
-        <v>35.98936295999999</v>
+        <v>35.814647034</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1727567903212236</v>
+        <v>0.1744005340753826</v>
       </c>
       <c r="T42">
-        <v>1.654672575319347</v>
+        <v>1.676096066760629</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.190997871596433</v>
+        <v>5.064388167411153</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4911,22 +4911,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1178604951044757</v>
+        <v>0.1174677160162173</v>
       </c>
       <c r="C43">
-        <v>356.7332531462812</v>
+        <v>354.9561770938128</v>
       </c>
       <c r="D43">
-        <v>549.2002531462813</v>
+        <v>552.2101770938128</v>
       </c>
       <c r="E43">
-        <v>95.36700000000002</v>
+        <v>100.154</v>
       </c>
       <c r="F43">
-        <v>196.267</v>
+        <v>201.054</v>
       </c>
       <c r="G43">
         <v>3.8</v>
@@ -4947,28 +4947,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M43">
-        <v>10.8535651</v>
+        <v>11.1182862</v>
       </c>
       <c r="N43">
-        <v>44.11310156666666</v>
+        <v>43.84838046666666</v>
       </c>
       <c r="O43">
-        <v>14.99845453266667</v>
+        <v>14.90844935866667</v>
       </c>
       <c r="P43">
-        <v>29.11464703399999</v>
+        <v>28.939931108</v>
       </c>
       <c r="Q43">
-        <v>35.814647034</v>
+        <v>35.639931108</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1744005340753826</v>
+        <v>0.1761009586486505</v>
       </c>
       <c r="T43">
-        <v>1.676096066760629</v>
+        <v>1.698258299286093</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4985,7 +4985,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.064388167411153</v>
+        <v>4.943807496758508</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1174677160162173</v>
+        <v>0.1170749369279589</v>
       </c>
       <c r="C44">
-        <v>354.9561770938127</v>
+        <v>353.2122749797521</v>
       </c>
       <c r="D44">
-        <v>552.2101770938127</v>
+        <v>555.2532749797522</v>
       </c>
       <c r="E44">
-        <v>100.154</v>
+        <v>104.941</v>
       </c>
       <c r="F44">
-        <v>201.054</v>
+        <v>205.841</v>
       </c>
       <c r="G44">
         <v>3.8</v>
@@ -5029,28 +5029,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M44">
-        <v>11.1182862</v>
+        <v>11.3830073</v>
       </c>
       <c r="N44">
-        <v>43.84838046666666</v>
+        <v>43.58365936666666</v>
       </c>
       <c r="O44">
-        <v>14.90844935866667</v>
+        <v>14.81844418466667</v>
       </c>
       <c r="P44">
-        <v>28.939931108</v>
+        <v>28.76521518199999</v>
       </c>
       <c r="Q44">
-        <v>35.639931108</v>
+        <v>35.46521518199999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1761009586486505</v>
+        <v>0.1778610472420331</v>
       </c>
       <c r="T44">
-        <v>1.698258299286092</v>
+        <v>1.721198154005432</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -5067,7 +5067,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.943807496758508</v>
+        <v>4.82883522939203</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5075,22 +5075,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1170749369279589</v>
+        <v>0.1166821578397004</v>
       </c>
       <c r="C45">
-        <v>353.2122749797521</v>
+        <v>351.5020982840354</v>
       </c>
       <c r="D45">
-        <v>555.2532749797522</v>
+        <v>558.3300982840354</v>
       </c>
       <c r="E45">
-        <v>104.941</v>
+        <v>109.728</v>
       </c>
       <c r="F45">
-        <v>205.841</v>
+        <v>210.628</v>
       </c>
       <c r="G45">
         <v>3.8</v>
@@ -5111,28 +5111,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M45">
-        <v>11.3830073</v>
+        <v>11.6477284</v>
       </c>
       <c r="N45">
-        <v>43.58365936666666</v>
+        <v>43.31893826666666</v>
       </c>
       <c r="O45">
-        <v>14.81844418466667</v>
+        <v>14.72843901066667</v>
       </c>
       <c r="P45">
-        <v>28.76521518199999</v>
+        <v>28.59049925599999</v>
       </c>
       <c r="Q45">
-        <v>35.46521518199999</v>
+        <v>35.290499256</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1778610472420331</v>
+        <v>0.1796839961423221</v>
       </c>
       <c r="T45">
-        <v>1.721198154005432</v>
+        <v>1.744957289250462</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.82883522939203</v>
+        <v>4.719088974178575</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5157,22 +5157,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1166821578397004</v>
+        <v>0.116289378751442</v>
       </c>
       <c r="C46">
-        <v>351.5020982840354</v>
+        <v>349.8262107783664</v>
       </c>
       <c r="D46">
-        <v>558.3300982840354</v>
+        <v>561.4412107783664</v>
       </c>
       <c r="E46">
-        <v>109.728</v>
+        <v>114.515</v>
       </c>
       <c r="F46">
-        <v>210.628</v>
+        <v>215.415</v>
       </c>
       <c r="G46">
         <v>3.8</v>
@@ -5193,28 +5193,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M46">
-        <v>11.6477284</v>
+        <v>11.9124495</v>
       </c>
       <c r="N46">
-        <v>43.31893826666666</v>
+        <v>43.05421716666666</v>
       </c>
       <c r="O46">
-        <v>14.72843901066667</v>
+        <v>14.63843383666667</v>
       </c>
       <c r="P46">
-        <v>28.59049925599999</v>
+        <v>28.41578333</v>
       </c>
       <c r="Q46">
-        <v>35.290499256</v>
+        <v>35.11578333</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1796839961423221</v>
+        <v>0.1815732340935308</v>
       </c>
       <c r="T46">
-        <v>1.744957289250462</v>
+        <v>1.769580393049857</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5231,7 +5231,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.719088974178575</v>
+        <v>4.614220330307941</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5239,22 +5239,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.116289378751442</v>
+        <v>0.1158965996631835</v>
       </c>
       <c r="C47">
-        <v>349.8262107783664</v>
+        <v>348.1851888705974</v>
       </c>
       <c r="D47">
-        <v>561.4412107783664</v>
+        <v>564.5871888705974</v>
       </c>
       <c r="E47">
-        <v>114.515</v>
+        <v>119.302</v>
       </c>
       <c r="F47">
-        <v>215.415</v>
+        <v>220.202</v>
       </c>
       <c r="G47">
         <v>3.8</v>
@@ -5275,28 +5275,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M47">
-        <v>11.9124495</v>
+        <v>12.1771706</v>
       </c>
       <c r="N47">
-        <v>43.05421716666666</v>
+        <v>42.78949606666666</v>
       </c>
       <c r="O47">
-        <v>14.63843383666667</v>
+        <v>14.54842866266666</v>
       </c>
       <c r="P47">
-        <v>28.41578333</v>
+        <v>28.24106740399999</v>
       </c>
       <c r="Q47">
-        <v>35.11578333</v>
+        <v>34.94106740399999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1815732340935308</v>
+        <v>0.1835324438207102</v>
       </c>
       <c r="T47">
-        <v>1.769580393049857</v>
+        <v>1.795115463656637</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5313,7 +5313,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.614220330307941</v>
+        <v>4.51391119269255</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5321,22 +5321,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1158965996631835</v>
+        <v>0.1162793205749251</v>
       </c>
       <c r="C48">
-        <v>348.1851888705974</v>
+        <v>340.3323346325097</v>
       </c>
       <c r="D48">
-        <v>564.5871888705974</v>
+        <v>561.5213346325098</v>
       </c>
       <c r="E48">
-        <v>119.302</v>
+        <v>124.089</v>
       </c>
       <c r="F48">
-        <v>220.202</v>
+        <v>224.989</v>
       </c>
       <c r="G48">
         <v>3.8</v>
@@ -5357,45 +5357,45 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M48">
-        <v>12.1771706</v>
+        <v>13.0043642</v>
       </c>
       <c r="N48">
-        <v>42.78949606666666</v>
+        <v>41.96230246666666</v>
       </c>
       <c r="O48">
-        <v>14.54842866266666</v>
+        <v>14.26718283866667</v>
       </c>
       <c r="P48">
-        <v>28.24106740399999</v>
+        <v>27.69511962799999</v>
       </c>
       <c r="Q48">
-        <v>34.94106740399999</v>
+        <v>34.395119628</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1835324438207102</v>
+        <v>0.1855655859904246</v>
       </c>
       <c r="T48">
-        <v>1.795115463656637</v>
+        <v>1.821614121833485</v>
       </c>
       <c r="U48">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V48">
         <v>0.34</v>
       </c>
       <c r="W48">
-        <v>0.036498</v>
+        <v>0.038148</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>4.51391119269255</v>
+        <v>4.226786163576275</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5403,22 +5403,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1162793205749251</v>
+        <v>0.1159030414866666</v>
       </c>
       <c r="C49">
-        <v>340.3323346325097</v>
+        <v>338.5593085108525</v>
       </c>
       <c r="D49">
-        <v>561.5213346325098</v>
+        <v>564.5353085108526</v>
       </c>
       <c r="E49">
-        <v>124.089</v>
+        <v>128.876</v>
       </c>
       <c r="F49">
-        <v>224.989</v>
+        <v>229.776</v>
       </c>
       <c r="G49">
         <v>3.8</v>
@@ -5439,28 +5439,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M49">
-        <v>13.0043642</v>
+        <v>13.2810528</v>
       </c>
       <c r="N49">
-        <v>41.96230246666666</v>
+        <v>41.68561386666666</v>
       </c>
       <c r="O49">
-        <v>14.26718283866667</v>
+        <v>14.17310871466666</v>
       </c>
       <c r="P49">
-        <v>27.69511962799999</v>
+        <v>27.51250515199999</v>
       </c>
       <c r="Q49">
-        <v>34.395119628</v>
+        <v>34.21250515199999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1855655859904246</v>
+        <v>0.1876769259358973</v>
       </c>
       <c r="T49">
-        <v>1.821614121833485</v>
+        <v>1.84913195917098</v>
       </c>
       <c r="U49">
         <v>0.0578</v>
@@ -5477,7 +5477,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.226786163576275</v>
+        <v>4.138728118501769</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5485,22 +5485,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1159030414866666</v>
+        <v>0.1155267623984082</v>
       </c>
       <c r="C50">
-        <v>338.5593085108525</v>
+        <v>336.8188120895275</v>
       </c>
       <c r="D50">
-        <v>564.5353085108526</v>
+        <v>567.5818120895275</v>
       </c>
       <c r="E50">
-        <v>128.876</v>
+        <v>133.663</v>
       </c>
       <c r="F50">
-        <v>229.776</v>
+        <v>234.563</v>
       </c>
       <c r="G50">
         <v>3.8</v>
@@ -5521,28 +5521,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M50">
-        <v>13.2810528</v>
+        <v>13.5577414</v>
       </c>
       <c r="N50">
-        <v>41.68561386666666</v>
+        <v>41.40892526666666</v>
       </c>
       <c r="O50">
-        <v>14.17310871466666</v>
+        <v>14.07903459066666</v>
       </c>
       <c r="P50">
-        <v>27.51250515199999</v>
+        <v>27.32989067599999</v>
       </c>
       <c r="Q50">
-        <v>34.21250515199999</v>
+        <v>34.02989067599999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1876769259358973</v>
+        <v>0.1898710635262905</v>
       </c>
       <c r="T50">
-        <v>1.84913195917098</v>
+        <v>1.877728927384455</v>
       </c>
       <c r="U50">
         <v>0.0578</v>
@@ -5559,7 +5559,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.138728118501769</v>
+        <v>4.054264279348672</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5567,22 +5567,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1155267623984082</v>
+        <v>0.1163054833101497</v>
       </c>
       <c r="C51">
-        <v>336.8188120895275</v>
+        <v>325.7629687961058</v>
       </c>
       <c r="D51">
-        <v>567.5818120895275</v>
+        <v>561.3129687961059</v>
       </c>
       <c r="E51">
-        <v>133.663</v>
+        <v>138.45</v>
       </c>
       <c r="F51">
-        <v>234.563</v>
+        <v>239.35</v>
       </c>
       <c r="G51">
         <v>3.8</v>
@@ -5603,45 +5603,45 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M51">
-        <v>13.5577414</v>
+        <v>14.672155</v>
       </c>
       <c r="N51">
-        <v>41.40892526666666</v>
+        <v>40.29451166666666</v>
       </c>
       <c r="O51">
-        <v>14.07903459066666</v>
+        <v>13.70013396666666</v>
       </c>
       <c r="P51">
-        <v>27.32989067599999</v>
+        <v>26.5943777</v>
       </c>
       <c r="Q51">
-        <v>34.02989067599999</v>
+        <v>33.2943777</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1898710635262905</v>
+        <v>0.1921529666202994</v>
       </c>
       <c r="T51">
-        <v>1.877728927384455</v>
+        <v>1.907469774326469</v>
       </c>
       <c r="U51">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V51">
         <v>0.34</v>
       </c>
       <c r="W51">
-        <v>0.038148</v>
+        <v>0.04045799999999999</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>4.054264279348672</v>
+        <v>3.746325380741047</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5649,22 +5649,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1163054833101497</v>
+        <v>0.1159523042218913</v>
       </c>
       <c r="C52">
-        <v>325.7629687961058</v>
+        <v>323.801877435115</v>
       </c>
       <c r="D52">
-        <v>561.3129687961059</v>
+        <v>564.1388774351151</v>
       </c>
       <c r="E52">
-        <v>138.45</v>
+        <v>143.237</v>
       </c>
       <c r="F52">
-        <v>239.35</v>
+        <v>244.137</v>
       </c>
       <c r="G52">
         <v>3.8</v>
@@ -5685,28 +5685,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M52">
-        <v>14.672155</v>
+        <v>14.9655981</v>
       </c>
       <c r="N52">
-        <v>40.29451166666666</v>
+        <v>40.00106856666666</v>
       </c>
       <c r="O52">
-        <v>13.70013396666666</v>
+        <v>13.60036331266667</v>
       </c>
       <c r="P52">
-        <v>26.5943777</v>
+        <v>26.40070525399999</v>
       </c>
       <c r="Q52">
-        <v>33.2943777</v>
+        <v>33.100705254</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1921529666202994</v>
+        <v>0.1945280086161047</v>
       </c>
       <c r="T52">
-        <v>1.907469774326469</v>
+        <v>1.938424533388566</v>
       </c>
       <c r="U52">
         <v>0.0613</v>
@@ -5723,7 +5723,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.746325380741047</v>
+        <v>3.67286802033436</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5731,22 +5731,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1159523042218913</v>
+        <v>0.1155991251336328</v>
       </c>
       <c r="C53">
-        <v>323.801877435115</v>
+        <v>321.8693839063957</v>
       </c>
       <c r="D53">
-        <v>564.1388774351151</v>
+        <v>566.9933839063958</v>
       </c>
       <c r="E53">
-        <v>143.237</v>
+        <v>148.024</v>
       </c>
       <c r="F53">
-        <v>244.137</v>
+        <v>248.924</v>
       </c>
       <c r="G53">
         <v>3.8</v>
@@ -5767,28 +5767,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M53">
-        <v>14.9655981</v>
+        <v>15.2590412</v>
       </c>
       <c r="N53">
-        <v>40.00106856666666</v>
+        <v>39.70762546666666</v>
       </c>
       <c r="O53">
-        <v>13.60036331266667</v>
+        <v>13.50059265866666</v>
       </c>
       <c r="P53">
-        <v>26.40070525399999</v>
+        <v>26.20703280799999</v>
       </c>
       <c r="Q53">
-        <v>33.100705254</v>
+        <v>32.907032808</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1945280086161047</v>
+        <v>0.1970020106950684</v>
       </c>
       <c r="T53">
-        <v>1.938424533388566</v>
+        <v>1.97066907407825</v>
       </c>
       <c r="U53">
         <v>0.0613</v>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.67286802033436</v>
+        <v>3.602235943020237</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5813,22 +5813,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1155991251336328</v>
+        <v>0.1152459460453744</v>
       </c>
       <c r="C54">
-        <v>321.8693839063957</v>
+        <v>319.9659245272663</v>
       </c>
       <c r="D54">
-        <v>566.9933839063958</v>
+        <v>569.8769245272664</v>
       </c>
       <c r="E54">
-        <v>148.024</v>
+        <v>152.811</v>
       </c>
       <c r="F54">
-        <v>248.924</v>
+        <v>253.711</v>
       </c>
       <c r="G54">
         <v>3.8</v>
@@ -5849,28 +5849,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M54">
-        <v>15.2590412</v>
+        <v>15.5524843</v>
       </c>
       <c r="N54">
-        <v>39.70762546666666</v>
+        <v>39.41418236666666</v>
       </c>
       <c r="O54">
-        <v>13.50059265866666</v>
+        <v>13.40082200466667</v>
       </c>
       <c r="P54">
-        <v>26.20703280799999</v>
+        <v>26.01336036199999</v>
       </c>
       <c r="Q54">
-        <v>32.907032808</v>
+        <v>32.713360362</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1970020106950684</v>
+        <v>0.1995812894582434</v>
       </c>
       <c r="T54">
-        <v>1.97066907407825</v>
+        <v>2.004285722882389</v>
       </c>
       <c r="U54">
         <v>0.0613</v>
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.602235943020237</v>
+        <v>3.534269227114195</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5895,22 +5895,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1152459460453744</v>
+        <v>0.1158906869571159</v>
       </c>
       <c r="C55">
-        <v>319.9659245272663</v>
+        <v>309.9368162836278</v>
       </c>
       <c r="D55">
-        <v>569.8769245272664</v>
+        <v>564.6348162836279</v>
       </c>
       <c r="E55">
-        <v>152.811</v>
+        <v>157.598</v>
       </c>
       <c r="F55">
-        <v>253.711</v>
+        <v>258.498</v>
       </c>
       <c r="G55">
         <v>3.8</v>
@@ -5931,45 +5931,45 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M55">
-        <v>15.5524843</v>
+        <v>16.5697218</v>
       </c>
       <c r="N55">
-        <v>39.41418236666666</v>
+        <v>38.39694486666666</v>
       </c>
       <c r="O55">
-        <v>13.40082200466667</v>
+        <v>13.05496125466667</v>
       </c>
       <c r="P55">
-        <v>26.01336036199999</v>
+        <v>25.34198361199999</v>
       </c>
       <c r="Q55">
-        <v>32.713360362</v>
+        <v>32.041983612</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1995812894582434</v>
+        <v>0.202272710776339</v>
       </c>
       <c r="T55">
-        <v>2.004285722882389</v>
+        <v>2.039363965112794</v>
       </c>
       <c r="U55">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V55">
         <v>0.34</v>
       </c>
       <c r="W55">
-        <v>0.04045799999999999</v>
+        <v>0.042306</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>3.534269227114195</v>
+        <v>3.317295687285869</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5977,22 +5977,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1158906869571159</v>
+        <v>0.1155559878688575</v>
       </c>
       <c r="C56">
-        <v>309.9368162836278</v>
+        <v>307.8590139307803</v>
       </c>
       <c r="D56">
-        <v>564.6348162836279</v>
+        <v>567.3440139307804</v>
       </c>
       <c r="E56">
-        <v>157.598</v>
+        <v>162.385</v>
       </c>
       <c r="F56">
-        <v>258.498</v>
+        <v>263.285</v>
       </c>
       <c r="G56">
         <v>3.8</v>
@@ -6013,28 +6013,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M56">
-        <v>16.5697218</v>
+        <v>16.8765685</v>
       </c>
       <c r="N56">
-        <v>38.39694486666666</v>
+        <v>38.09009816666666</v>
       </c>
       <c r="O56">
-        <v>13.05496125466667</v>
+        <v>12.95063337666667</v>
       </c>
       <c r="P56">
-        <v>25.34198361199999</v>
+        <v>25.13946479</v>
       </c>
       <c r="Q56">
-        <v>32.041983612</v>
+        <v>31.83946479</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.202272710776339</v>
+        <v>0.2050837508196833</v>
       </c>
       <c r="T56">
-        <v>2.039363965112794</v>
+        <v>2.076001240331218</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -6051,7 +6051,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.317295687285869</v>
+        <v>3.256981220244309</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1155559878688575</v>
+        <v>0.1152212887805991</v>
       </c>
       <c r="C57">
-        <v>307.8590139307803</v>
+        <v>305.8073351489105</v>
       </c>
       <c r="D57">
-        <v>567.3440139307804</v>
+        <v>570.0793351489106</v>
       </c>
       <c r="E57">
-        <v>162.385</v>
+        <v>167.1720000000001</v>
       </c>
       <c r="F57">
-        <v>263.285</v>
+        <v>268.0720000000001</v>
       </c>
       <c r="G57">
         <v>3.8</v>
@@ -6095,28 +6095,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M57">
-        <v>16.8765685</v>
+        <v>17.18341520000001</v>
       </c>
       <c r="N57">
-        <v>38.09009816666666</v>
+        <v>37.78325146666666</v>
       </c>
       <c r="O57">
-        <v>12.95063337666667</v>
+        <v>12.84630549866666</v>
       </c>
       <c r="P57">
-        <v>25.13946479</v>
+        <v>24.93694596799999</v>
       </c>
       <c r="Q57">
-        <v>31.83946479</v>
+        <v>31.63694596799999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2050837508196833</v>
+        <v>0.2080225654104524</v>
       </c>
       <c r="T57">
-        <v>2.076001240331218</v>
+        <v>2.114303846241388</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -6133,7 +6133,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.256981220244309</v>
+        <v>3.198820841311373</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6141,22 +6141,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1152212887805991</v>
+        <v>0.1148865896923406</v>
       </c>
       <c r="C58">
-        <v>305.8073351489105</v>
+        <v>303.7821596152654</v>
       </c>
       <c r="D58">
-        <v>570.0793351489106</v>
+        <v>572.8411596152655</v>
       </c>
       <c r="E58">
-        <v>167.1720000000001</v>
+        <v>171.959</v>
       </c>
       <c r="F58">
-        <v>268.0720000000001</v>
+        <v>272.859</v>
       </c>
       <c r="G58">
         <v>3.8</v>
@@ -6177,28 +6177,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M58">
-        <v>17.18341520000001</v>
+        <v>17.4902619</v>
       </c>
       <c r="N58">
-        <v>37.78325146666666</v>
+        <v>37.47640476666666</v>
       </c>
       <c r="O58">
-        <v>12.84630549866666</v>
+        <v>12.74197762066667</v>
       </c>
       <c r="P58">
-        <v>24.93694596799999</v>
+        <v>24.73442714599999</v>
       </c>
       <c r="Q58">
-        <v>31.63694596799999</v>
+        <v>31.434427146</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2080225654104524</v>
+        <v>0.2110980690519549</v>
       </c>
       <c r="T58">
-        <v>2.114303846241388</v>
+        <v>2.15438796870552</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6215,7 +6215,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.198820841311373</v>
+        <v>3.142701177428719</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6223,22 +6223,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1148865896923406</v>
+        <v>0.1145518906040821</v>
       </c>
       <c r="C59">
-        <v>303.7821596152654</v>
+        <v>301.7838744004956</v>
       </c>
       <c r="D59">
-        <v>572.8411596152655</v>
+        <v>575.6298744004957</v>
       </c>
       <c r="E59">
-        <v>171.959</v>
+        <v>176.7460000000001</v>
       </c>
       <c r="F59">
-        <v>272.859</v>
+        <v>277.6460000000001</v>
       </c>
       <c r="G59">
         <v>3.8</v>
@@ -6259,28 +6259,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M59">
-        <v>17.4902619</v>
+        <v>17.7971086</v>
       </c>
       <c r="N59">
-        <v>37.47640476666666</v>
+        <v>37.16955806666665</v>
       </c>
       <c r="O59">
-        <v>12.74197762066667</v>
+        <v>12.63764974266666</v>
       </c>
       <c r="P59">
-        <v>24.73442714599999</v>
+        <v>24.53190832399999</v>
       </c>
       <c r="Q59">
-        <v>31.434427146</v>
+        <v>31.231908324</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2110980690519549</v>
+        <v>0.2143200252478147</v>
       </c>
       <c r="T59">
-        <v>2.15438796870552</v>
+        <v>2.196380858906038</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6297,7 +6297,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.142701177428719</v>
+        <v>3.088516674369602</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6305,22 +6305,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1145518906040822</v>
+        <v>0.1142171915158237</v>
       </c>
       <c r="C60">
-        <v>301.7838744004956</v>
+        <v>299.8128741495004</v>
       </c>
       <c r="D60">
-        <v>575.6298744004956</v>
+        <v>578.4458741495005</v>
       </c>
       <c r="E60">
-        <v>176.746</v>
+        <v>181.533</v>
       </c>
       <c r="F60">
-        <v>277.646</v>
+        <v>282.433</v>
       </c>
       <c r="G60">
         <v>3.8</v>
@@ -6341,28 +6341,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M60">
-        <v>17.7971086</v>
+        <v>18.1039553</v>
       </c>
       <c r="N60">
-        <v>37.16955806666666</v>
+        <v>36.86271136666666</v>
       </c>
       <c r="O60">
-        <v>12.63764974266667</v>
+        <v>12.53332186466666</v>
       </c>
       <c r="P60">
-        <v>24.53190832399999</v>
+        <v>24.32938950199999</v>
       </c>
       <c r="Q60">
-        <v>31.231908324</v>
+        <v>31.029389502</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2143200252478147</v>
+        <v>0.2176991500385944</v>
       </c>
       <c r="T60">
-        <v>2.196380858906038</v>
+        <v>2.240422182774874</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6379,7 +6379,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.088516674369603</v>
+        <v>3.03616893412605</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6387,22 +6387,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1142171915158237</v>
+        <v>0.1169712924275653</v>
       </c>
       <c r="C61">
-        <v>299.8128741495004</v>
+        <v>272.6418727488</v>
       </c>
       <c r="D61">
-        <v>578.4458741495005</v>
+        <v>556.0618727488001</v>
       </c>
       <c r="E61">
-        <v>181.533</v>
+        <v>186.32</v>
       </c>
       <c r="F61">
-        <v>282.433</v>
+        <v>287.22</v>
       </c>
       <c r="G61">
         <v>3.8</v>
@@ -6423,45 +6423,45 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M61">
-        <v>18.1039553</v>
+        <v>20.651118</v>
       </c>
       <c r="N61">
-        <v>36.86271136666666</v>
+        <v>34.31554866666666</v>
       </c>
       <c r="O61">
-        <v>12.53332186466666</v>
+        <v>11.66728654666666</v>
       </c>
       <c r="P61">
-        <v>24.32938950199999</v>
+        <v>22.64826211999999</v>
       </c>
       <c r="Q61">
-        <v>31.029389502</v>
+        <v>29.34826211999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2176991500385944</v>
+        <v>0.2212472310689132</v>
       </c>
       <c r="T61">
-        <v>2.240422182774874</v>
+        <v>2.286665572837153</v>
       </c>
       <c r="U61">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V61">
         <v>0.34</v>
       </c>
       <c r="W61">
-        <v>0.042306</v>
+        <v>0.047454</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y61">
-        <v>3.03616893412605</v>
+        <v>2.661679947142167</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6469,22 +6469,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1169712924275653</v>
+        <v>0.1166880733393068</v>
       </c>
       <c r="C62">
-        <v>272.6418727488</v>
+        <v>270.0765065046135</v>
       </c>
       <c r="D62">
-        <v>556.0618727488001</v>
+        <v>558.2835065046136</v>
       </c>
       <c r="E62">
-        <v>186.32</v>
+        <v>191.107</v>
       </c>
       <c r="F62">
-        <v>287.22</v>
+        <v>292.007</v>
       </c>
       <c r="G62">
         <v>3.8</v>
@@ -6505,28 +6505,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M62">
-        <v>20.651118</v>
+        <v>20.9953033</v>
       </c>
       <c r="N62">
-        <v>34.31554866666666</v>
+        <v>33.97136336666666</v>
       </c>
       <c r="O62">
-        <v>11.66728654666666</v>
+        <v>11.55026354466666</v>
       </c>
       <c r="P62">
-        <v>22.64826211999999</v>
+        <v>22.421099822</v>
       </c>
       <c r="Q62">
-        <v>29.34826211999999</v>
+        <v>29.121099822</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2212472310689132</v>
+        <v>0.2249772649725816</v>
       </c>
       <c r="T62">
-        <v>2.286665572837153</v>
+        <v>2.335280418800062</v>
       </c>
       <c r="U62">
         <v>0.07190000000000001</v>
@@ -6543,7 +6543,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.661679947142167</v>
+        <v>2.618045849648033</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6551,22 +6551,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1166880733393068</v>
+        <v>0.1164048542510484</v>
       </c>
       <c r="C63">
-        <v>270.0765065046135</v>
+        <v>267.5289636549639</v>
       </c>
       <c r="D63">
-        <v>558.2835065046136</v>
+        <v>560.522963654964</v>
       </c>
       <c r="E63">
-        <v>191.107</v>
+        <v>195.894</v>
       </c>
       <c r="F63">
-        <v>292.007</v>
+        <v>296.794</v>
       </c>
       <c r="G63">
         <v>3.8</v>
@@ -6587,28 +6587,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M63">
-        <v>20.9953033</v>
+        <v>21.3394886</v>
       </c>
       <c r="N63">
-        <v>33.97136336666666</v>
+        <v>33.62717806666666</v>
       </c>
       <c r="O63">
-        <v>11.55026354466666</v>
+        <v>11.43324054266667</v>
       </c>
       <c r="P63">
-        <v>22.421099822</v>
+        <v>22.19393752399999</v>
       </c>
       <c r="Q63">
-        <v>29.121099822</v>
+        <v>28.89393752399999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2249772649725816</v>
+        <v>0.2289036164501273</v>
       </c>
       <c r="T63">
-        <v>2.335280418800062</v>
+        <v>2.38645394086628</v>
       </c>
       <c r="U63">
         <v>0.07190000000000001</v>
@@ -6625,7 +6625,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.618045849648033</v>
+        <v>2.575819303685968</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6633,22 +6633,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1164048542510484</v>
+        <v>0.1161216351627899</v>
       </c>
       <c r="C64">
-        <v>267.5289636549639</v>
+        <v>264.9994595500293</v>
       </c>
       <c r="D64">
-        <v>560.522963654964</v>
+        <v>562.7804595500294</v>
       </c>
       <c r="E64">
-        <v>195.894</v>
+        <v>200.681</v>
       </c>
       <c r="F64">
-        <v>296.794</v>
+        <v>301.581</v>
       </c>
       <c r="G64">
         <v>3.8</v>
@@ -6669,28 +6669,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M64">
-        <v>21.3394886</v>
+        <v>21.6836739</v>
       </c>
       <c r="N64">
-        <v>33.62717806666666</v>
+        <v>33.28299276666666</v>
       </c>
       <c r="O64">
-        <v>11.43324054266667</v>
+        <v>11.31621754066667</v>
       </c>
       <c r="P64">
-        <v>22.19393752399999</v>
+        <v>21.966775226</v>
       </c>
       <c r="Q64">
-        <v>28.89393752399999</v>
+        <v>28.666775226</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2289036164501273</v>
+        <v>0.2330422031426755</v>
       </c>
       <c r="T64">
-        <v>2.38645394086628</v>
+        <v>2.440393599260403</v>
       </c>
       <c r="U64">
         <v>0.07190000000000001</v>
@@ -6707,7 +6707,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.575819303685968</v>
+        <v>2.53493328299254</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6715,22 +6715,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1161216351627899</v>
+        <v>0.1174857760745315</v>
       </c>
       <c r="C65">
-        <v>264.9994595500293</v>
+        <v>249.5030567753045</v>
       </c>
       <c r="D65">
-        <v>562.7804595500294</v>
+        <v>552.0710567753046</v>
       </c>
       <c r="E65">
-        <v>200.681</v>
+        <v>205.468</v>
       </c>
       <c r="F65">
-        <v>301.581</v>
+        <v>306.3680000000001</v>
       </c>
       <c r="G65">
         <v>3.8</v>
@@ -6751,45 +6751,45 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M65">
-        <v>21.6836739</v>
+        <v>23.22269440000001</v>
       </c>
       <c r="N65">
-        <v>33.28299276666666</v>
+        <v>31.74397226666666</v>
       </c>
       <c r="O65">
-        <v>11.31621754066667</v>
+        <v>10.79295057066666</v>
       </c>
       <c r="P65">
-        <v>21.966775226</v>
+        <v>20.95102169599999</v>
       </c>
       <c r="Q65">
-        <v>28.666775226</v>
+        <v>27.65102169599999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2330422031426755</v>
+        <v>0.237410711318143</v>
       </c>
       <c r="T65">
-        <v>2.440393599260403</v>
+        <v>2.497329905343089</v>
       </c>
       <c r="U65">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V65">
         <v>0.34</v>
       </c>
       <c r="W65">
-        <v>0.047454</v>
+        <v>0.050028</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y65">
-        <v>2.53493328299254</v>
+        <v>2.366937518958466</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6797,22 +6797,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1174857760745315</v>
+        <v>0.1172282969862731</v>
       </c>
       <c r="C66">
-        <v>249.5030567753045</v>
+        <v>246.7061189544389</v>
       </c>
       <c r="D66">
-        <v>552.0710567753046</v>
+        <v>554.0611189544389</v>
       </c>
       <c r="E66">
-        <v>205.468</v>
+        <v>210.255</v>
       </c>
       <c r="F66">
-        <v>306.3680000000001</v>
+        <v>311.155</v>
       </c>
       <c r="G66">
         <v>3.8</v>
@@ -6833,28 +6833,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M66">
-        <v>23.22269440000001</v>
+        <v>23.585549</v>
       </c>
       <c r="N66">
-        <v>31.74397226666666</v>
+        <v>31.38111766666666</v>
       </c>
       <c r="O66">
-        <v>10.79295057066666</v>
+        <v>10.66958000666666</v>
       </c>
       <c r="P66">
-        <v>20.95102169599999</v>
+        <v>20.71153765999999</v>
       </c>
       <c r="Q66">
-        <v>27.65102169599999</v>
+        <v>27.41153766</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.237410711318143</v>
+        <v>0.2420288485322088</v>
       </c>
       <c r="T66">
-        <v>2.497329905343089</v>
+        <v>2.557519714630499</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6871,7 +6871,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.366937518958466</v>
+        <v>2.330523095589874</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6879,22 +6879,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1172282969862731</v>
+        <v>0.1169708178980146</v>
       </c>
       <c r="C67">
-        <v>246.7061189544389</v>
+        <v>243.9235802766662</v>
       </c>
       <c r="D67">
-        <v>554.0611189544389</v>
+        <v>556.0655802766663</v>
       </c>
       <c r="E67">
-        <v>210.255</v>
+        <v>215.0420000000001</v>
       </c>
       <c r="F67">
-        <v>311.155</v>
+        <v>315.9420000000001</v>
       </c>
       <c r="G67">
         <v>3.8</v>
@@ -6915,28 +6915,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M67">
-        <v>23.585549</v>
+        <v>23.94840360000001</v>
       </c>
       <c r="N67">
-        <v>31.38111766666666</v>
+        <v>31.01826306666666</v>
       </c>
       <c r="O67">
-        <v>10.66958000666666</v>
+        <v>10.54620944266666</v>
       </c>
       <c r="P67">
-        <v>20.71153765999999</v>
+        <v>20.47205362399999</v>
       </c>
       <c r="Q67">
-        <v>27.41153766</v>
+        <v>27.17205362399999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2420288485322088</v>
+        <v>0.2469186408765136</v>
       </c>
       <c r="T67">
-        <v>2.557519714630499</v>
+        <v>2.621250100934815</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.330523095589874</v>
+        <v>2.295212139596088</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6961,22 +6961,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1169708178980146</v>
+        <v>0.1167133388097562</v>
       </c>
       <c r="C68">
-        <v>243.9235802766662</v>
+        <v>241.1555975874383</v>
       </c>
       <c r="D68">
-        <v>556.0655802766663</v>
+        <v>558.0845975874383</v>
       </c>
       <c r="E68">
-        <v>215.0420000000001</v>
+        <v>219.829</v>
       </c>
       <c r="F68">
-        <v>315.9420000000001</v>
+        <v>320.729</v>
       </c>
       <c r="G68">
         <v>3.8</v>
@@ -6997,28 +6997,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M68">
-        <v>23.94840360000001</v>
+        <v>24.3112582</v>
       </c>
       <c r="N68">
-        <v>31.01826306666666</v>
+        <v>30.65540846666666</v>
       </c>
       <c r="O68">
-        <v>10.54620944266666</v>
+        <v>10.42283887866666</v>
       </c>
       <c r="P68">
-        <v>20.47205362399999</v>
+        <v>20.23256958799999</v>
       </c>
       <c r="Q68">
-        <v>27.17205362399999</v>
+        <v>26.932569588</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2469186408765136</v>
+        <v>0.2521047842719883</v>
       </c>
       <c r="T68">
-        <v>2.621250100934815</v>
+        <v>2.688842934893939</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.295212139596088</v>
+        <v>2.260955241990176</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7043,22 +7043,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1167133388097562</v>
+        <v>0.1164558597214977</v>
       </c>
       <c r="C69">
-        <v>241.1555975874383</v>
+        <v>238.4023300184679</v>
       </c>
       <c r="D69">
-        <v>558.0845975874383</v>
+        <v>560.118330018468</v>
       </c>
       <c r="E69">
-        <v>219.829</v>
+        <v>224.6160000000001</v>
       </c>
       <c r="F69">
-        <v>320.729</v>
+        <v>325.5160000000001</v>
       </c>
       <c r="G69">
         <v>3.8</v>
@@ -7079,28 +7079,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M69">
-        <v>24.3112582</v>
+        <v>24.67411280000001</v>
       </c>
       <c r="N69">
-        <v>30.65540846666666</v>
+        <v>30.29255386666665</v>
       </c>
       <c r="O69">
-        <v>10.42283887866666</v>
+        <v>10.29946831466666</v>
       </c>
       <c r="P69">
-        <v>20.23256958799999</v>
+        <v>19.99308555199999</v>
       </c>
       <c r="Q69">
-        <v>26.932569588</v>
+        <v>26.69308555199999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2521047842719883</v>
+        <v>0.2576150616296803</v>
       </c>
       <c r="T69">
-        <v>2.688842934893939</v>
+        <v>2.760660320975508</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -7117,7 +7117,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.260955241990176</v>
+        <v>2.227705900196203</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7125,22 +7125,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1164558597214977</v>
+        <v>0.1161983806332393</v>
       </c>
       <c r="C70">
-        <v>238.4023300184679</v>
+        <v>235.663939029538</v>
       </c>
       <c r="D70">
-        <v>560.118330018468</v>
+        <v>562.1669390295381</v>
       </c>
       <c r="E70">
-        <v>224.6160000000001</v>
+        <v>229.403</v>
       </c>
       <c r="F70">
-        <v>325.5160000000001</v>
+        <v>330.3030000000001</v>
       </c>
       <c r="G70">
         <v>3.8</v>
@@ -7161,28 +7161,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M70">
-        <v>24.67411280000001</v>
+        <v>25.03696740000001</v>
       </c>
       <c r="N70">
-        <v>30.29255386666665</v>
+        <v>29.92969926666666</v>
       </c>
       <c r="O70">
-        <v>10.29946831466666</v>
+        <v>10.17609775066666</v>
       </c>
       <c r="P70">
-        <v>19.99308555199999</v>
+        <v>19.75360151599999</v>
       </c>
       <c r="Q70">
-        <v>26.69308555199999</v>
+        <v>26.453601516</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2576150616296803</v>
+        <v>0.2634808407523848</v>
       </c>
       <c r="T70">
-        <v>2.760660320975508</v>
+        <v>2.837111086804275</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7199,7 +7199,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.227705900196203</v>
+        <v>2.195420307439736</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7207,22 +7207,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1161983806332393</v>
+        <v>0.1159409015449808</v>
       </c>
       <c r="C71">
-        <v>235.663939029538</v>
+        <v>232.9405884512316</v>
       </c>
       <c r="D71">
-        <v>562.1669390295381</v>
+        <v>564.2305884512317</v>
       </c>
       <c r="E71">
-        <v>229.403</v>
+        <v>234.1900000000001</v>
       </c>
       <c r="F71">
-        <v>330.3030000000001</v>
+        <v>335.0900000000001</v>
       </c>
       <c r="G71">
         <v>3.8</v>
@@ -7243,28 +7243,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M71">
-        <v>25.03696740000001</v>
+        <v>25.39982200000001</v>
       </c>
       <c r="N71">
-        <v>29.92969926666666</v>
+        <v>29.56684466666665</v>
       </c>
       <c r="O71">
-        <v>10.17609775066666</v>
+        <v>10.05272718666666</v>
       </c>
       <c r="P71">
-        <v>19.75360151599999</v>
+        <v>19.51411747999999</v>
       </c>
       <c r="Q71">
-        <v>26.453601516</v>
+        <v>26.21411747999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2634808407523848</v>
+        <v>0.2697376718166027</v>
       </c>
       <c r="T71">
-        <v>2.837111086804275</v>
+        <v>2.918658570354959</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7281,7 +7281,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.195420307439736</v>
+        <v>2.164057160190597</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7289,22 +7289,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1159409015449808</v>
+        <v>0.1156834224567224</v>
       </c>
       <c r="C72">
-        <v>232.9405884512316</v>
+        <v>230.2324445286068</v>
       </c>
       <c r="D72">
-        <v>564.2305884512317</v>
+        <v>566.3094445286069</v>
       </c>
       <c r="E72">
-        <v>234.1900000000001</v>
+        <v>238.9770000000001</v>
       </c>
       <c r="F72">
-        <v>335.0900000000001</v>
+        <v>339.8770000000001</v>
       </c>
       <c r="G72">
         <v>3.8</v>
@@ -7325,28 +7325,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M72">
-        <v>25.39982200000001</v>
+        <v>25.76267660000001</v>
       </c>
       <c r="N72">
-        <v>29.56684466666665</v>
+        <v>29.20399006666666</v>
       </c>
       <c r="O72">
-        <v>10.05272718666666</v>
+        <v>9.929356622666663</v>
       </c>
       <c r="P72">
-        <v>19.51411747999999</v>
+        <v>19.27463344399999</v>
       </c>
       <c r="Q72">
-        <v>26.21411747999999</v>
+        <v>25.97463344399999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2697376718166027</v>
+        <v>0.2764260084714565</v>
       </c>
       <c r="T72">
-        <v>2.918658570354959</v>
+        <v>3.005830018288451</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7363,7 +7363,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.164057160190597</v>
+        <v>2.133577481878053</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7371,22 +7371,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1156834224567224</v>
+        <v>0.1154259433684639</v>
       </c>
       <c r="C73">
-        <v>230.2324445286071</v>
+        <v>227.5396759658418</v>
       </c>
       <c r="D73">
-        <v>566.3094445286072</v>
+        <v>568.4036759658419</v>
       </c>
       <c r="E73">
-        <v>238.977</v>
+        <v>243.764</v>
       </c>
       <c r="F73">
-        <v>339.877</v>
+        <v>344.664</v>
       </c>
       <c r="G73">
         <v>3.8</v>
@@ -7407,28 +7407,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M73">
-        <v>25.7626766</v>
+        <v>26.1255312</v>
       </c>
       <c r="N73">
-        <v>29.20399006666666</v>
+        <v>28.84113546666666</v>
       </c>
       <c r="O73">
-        <v>9.929356622666665</v>
+        <v>9.805986058666663</v>
       </c>
       <c r="P73">
-        <v>19.274633444</v>
+        <v>19.035149408</v>
       </c>
       <c r="Q73">
-        <v>25.974633444</v>
+        <v>25.735149408</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2764260084714564</v>
+        <v>0.2835920834587997</v>
       </c>
       <c r="T73">
-        <v>3.005830018288449</v>
+        <v>3.099227998217189</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7445,7 +7445,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.133577481878054</v>
+        <v>2.103944461296414</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7453,22 +7453,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1154259433684639</v>
+        <v>0.1151684642802055</v>
       </c>
       <c r="C74">
-        <v>227.5396759658418</v>
+        <v>224.8624539718717</v>
       </c>
       <c r="D74">
-        <v>568.4036759658419</v>
+        <v>570.5134539718717</v>
       </c>
       <c r="E74">
-        <v>243.764</v>
+        <v>248.551</v>
       </c>
       <c r="F74">
-        <v>344.664</v>
+        <v>349.451</v>
       </c>
       <c r="G74">
         <v>3.8</v>
@@ -7489,28 +7489,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M74">
-        <v>26.1255312</v>
+        <v>26.4883858</v>
       </c>
       <c r="N74">
-        <v>28.84113546666666</v>
+        <v>28.47828086666666</v>
       </c>
       <c r="O74">
-        <v>9.805986058666663</v>
+        <v>9.682615494666665</v>
       </c>
       <c r="P74">
-        <v>19.035149408</v>
+        <v>18.79566537199999</v>
       </c>
       <c r="Q74">
-        <v>25.735149408</v>
+        <v>25.495665372</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2835920834587997</v>
+        <v>0.2912889788155759</v>
       </c>
       <c r="T74">
-        <v>3.099227998217189</v>
+        <v>3.19954434702954</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.103944461296414</v>
+        <v>2.075123304292354</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7535,22 +7535,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1151684642802055</v>
+        <v>0.1149109851919471</v>
       </c>
       <c r="C75">
-        <v>224.8624539718717</v>
+        <v>222.2009523070473</v>
       </c>
       <c r="D75">
-        <v>570.5134539718717</v>
+        <v>572.6389523070474</v>
       </c>
       <c r="E75">
-        <v>248.551</v>
+        <v>253.3380000000001</v>
       </c>
       <c r="F75">
-        <v>349.451</v>
+        <v>354.2380000000001</v>
       </c>
       <c r="G75">
         <v>3.8</v>
@@ -7571,28 +7571,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M75">
-        <v>26.4883858</v>
+        <v>26.85124040000001</v>
       </c>
       <c r="N75">
-        <v>28.47828086666666</v>
+        <v>28.11542626666666</v>
       </c>
       <c r="O75">
-        <v>9.682615494666665</v>
+        <v>9.559244930666663</v>
       </c>
       <c r="P75">
-        <v>18.79566537199999</v>
+        <v>18.55618133599999</v>
       </c>
       <c r="Q75">
-        <v>25.495665372</v>
+        <v>25.256181336</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2912889788155759</v>
+        <v>0.2995779430459502</v>
       </c>
       <c r="T75">
-        <v>3.19954434702954</v>
+        <v>3.307577338058225</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7609,7 +7609,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.075123304292354</v>
+        <v>2.047081097477592</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7617,22 +7617,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1149109851919471</v>
+        <v>0.1146535061036886</v>
       </c>
       <c r="C76">
-        <v>222.2009523070473</v>
+        <v>219.5553473308426</v>
       </c>
       <c r="D76">
-        <v>572.6389523070474</v>
+        <v>574.7803473308427</v>
       </c>
       <c r="E76">
-        <v>253.3380000000001</v>
+        <v>258.125</v>
       </c>
       <c r="F76">
-        <v>354.2380000000001</v>
+        <v>359.025</v>
       </c>
       <c r="G76">
         <v>3.8</v>
@@ -7653,28 +7653,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M76">
-        <v>26.85124040000001</v>
+        <v>27.214095</v>
       </c>
       <c r="N76">
-        <v>28.11542626666666</v>
+        <v>27.75257166666666</v>
       </c>
       <c r="O76">
-        <v>9.559244930666663</v>
+        <v>9.435874366666665</v>
       </c>
       <c r="P76">
-        <v>18.55618133599999</v>
+        <v>18.31669729999999</v>
       </c>
       <c r="Q76">
-        <v>25.256181336</v>
+        <v>25.0166973</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2995779430459502</v>
+        <v>0.3085300244147544</v>
       </c>
       <c r="T76">
-        <v>3.307577338058225</v>
+        <v>3.424252968369204</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7691,7 +7691,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.047081097477592</v>
+        <v>2.019786682844558</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7699,22 +7699,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1146535061036886</v>
+        <v>0.1215187470154302</v>
       </c>
       <c r="C77">
-        <v>219.5553473308426</v>
+        <v>162.6543635250014</v>
       </c>
       <c r="D77">
-        <v>574.7803473308427</v>
+        <v>522.6663635250014</v>
       </c>
       <c r="E77">
-        <v>258.125</v>
+        <v>262.912</v>
       </c>
       <c r="F77">
-        <v>359.025</v>
+        <v>363.812</v>
       </c>
       <c r="G77">
         <v>3.8</v>
@@ -7735,45 +7735,45 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M77">
-        <v>27.214095</v>
+        <v>32.74308</v>
       </c>
       <c r="N77">
-        <v>27.75257166666666</v>
+        <v>22.22358666666666</v>
       </c>
       <c r="O77">
-        <v>9.435874366666665</v>
+        <v>7.556019466666665</v>
       </c>
       <c r="P77">
-        <v>18.31669729999999</v>
+        <v>14.6675672</v>
       </c>
       <c r="Q77">
-        <v>25.0166973</v>
+        <v>21.3675672</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3085300244147544</v>
+        <v>0.3182281125642923</v>
       </c>
       <c r="T77">
-        <v>3.424252968369204</v>
+        <v>3.550651567872765</v>
       </c>
       <c r="U77">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V77">
         <v>0.34</v>
       </c>
       <c r="W77">
-        <v>0.050028</v>
+        <v>0.05939999999999999</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y77">
-        <v>2.019786682844558</v>
+        <v>1.678726212276507</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7781,22 +7781,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1215187470154302</v>
+        <v>0.1213549879271717</v>
       </c>
       <c r="C78">
-        <v>162.6543635250014</v>
+        <v>159.000198953904</v>
       </c>
       <c r="D78">
-        <v>522.6663635250014</v>
+        <v>523.7991989539041</v>
       </c>
       <c r="E78">
-        <v>262.912</v>
+        <v>267.6990000000001</v>
       </c>
       <c r="F78">
-        <v>363.812</v>
+        <v>368.599</v>
       </c>
       <c r="G78">
         <v>3.8</v>
@@ -7817,28 +7817,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M78">
-        <v>32.74308</v>
+        <v>33.17391000000001</v>
       </c>
       <c r="N78">
-        <v>22.22358666666666</v>
+        <v>21.79275666666666</v>
       </c>
       <c r="O78">
-        <v>7.556019466666665</v>
+        <v>7.409537266666663</v>
       </c>
       <c r="P78">
-        <v>14.6675672</v>
+        <v>14.38321939999999</v>
       </c>
       <c r="Q78">
-        <v>21.3675672</v>
+        <v>21.08321939999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3182281125642923</v>
+        <v>0.3287695127268335</v>
       </c>
       <c r="T78">
-        <v>3.550651567872765</v>
+        <v>3.688041349941854</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7855,7 +7855,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.678726212276507</v>
+        <v>1.656924573156033</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7863,22 +7863,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1213549879271717</v>
+        <v>0.1211912288389133</v>
       </c>
       <c r="C79">
-        <v>159.000198953904</v>
+        <v>155.3509557005738</v>
       </c>
       <c r="D79">
-        <v>523.7991989539041</v>
+        <v>524.9369557005739</v>
       </c>
       <c r="E79">
-        <v>267.6990000000001</v>
+        <v>272.486</v>
       </c>
       <c r="F79">
-        <v>368.599</v>
+        <v>373.386</v>
       </c>
       <c r="G79">
         <v>3.8</v>
@@ -7899,28 +7899,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M79">
-        <v>33.17391000000001</v>
+        <v>33.60474</v>
       </c>
       <c r="N79">
-        <v>21.79275666666666</v>
+        <v>21.36192666666666</v>
       </c>
       <c r="O79">
-        <v>7.409537266666663</v>
+        <v>7.263055066666666</v>
       </c>
       <c r="P79">
-        <v>14.38321939999999</v>
+        <v>14.0988716</v>
       </c>
       <c r="Q79">
-        <v>21.08321939999999</v>
+        <v>20.7988716</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3287695127268335</v>
+        <v>0.3402692219950603</v>
       </c>
       <c r="T79">
-        <v>3.688041349941854</v>
+        <v>3.837921112199041</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7937,7 +7937,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.656924573156033</v>
+        <v>1.635681950423264</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7945,22 +7945,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1211912288389133</v>
+        <v>0.1210274697506548</v>
       </c>
       <c r="C80">
-        <v>155.3509557005738</v>
+        <v>151.7066659039558</v>
       </c>
       <c r="D80">
-        <v>524.9369557005739</v>
+        <v>526.0796659039559</v>
       </c>
       <c r="E80">
-        <v>272.486</v>
+        <v>277.273</v>
       </c>
       <c r="F80">
-        <v>373.386</v>
+        <v>378.1730000000001</v>
       </c>
       <c r="G80">
         <v>3.8</v>
@@ -7981,28 +7981,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M80">
-        <v>33.60474</v>
+        <v>34.03557000000001</v>
       </c>
       <c r="N80">
-        <v>21.36192666666666</v>
+        <v>20.93109666666665</v>
       </c>
       <c r="O80">
-        <v>7.263055066666666</v>
+        <v>7.116572866666663</v>
       </c>
       <c r="P80">
-        <v>14.0988716</v>
+        <v>13.81452379999999</v>
       </c>
       <c r="Q80">
-        <v>20.7988716</v>
+        <v>20.51452379999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3402692219950603</v>
+        <v>0.3528641416697849</v>
       </c>
       <c r="T80">
-        <v>3.837921112199041</v>
+        <v>4.002075137528342</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -8019,7 +8019,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.635681950423264</v>
+        <v>1.614977115607779</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8027,22 +8027,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1210274697506548</v>
+        <v>0.1208637106623964</v>
       </c>
       <c r="C81">
-        <v>151.7066659039558</v>
+        <v>148.067361983453</v>
       </c>
       <c r="D81">
-        <v>526.0796659039559</v>
+        <v>527.2273619834531</v>
       </c>
       <c r="E81">
-        <v>277.273</v>
+        <v>282.0600000000001</v>
       </c>
       <c r="F81">
-        <v>378.1730000000001</v>
+        <v>382.96</v>
       </c>
       <c r="G81">
         <v>3.8</v>
@@ -8063,28 +8063,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M81">
-        <v>34.03557000000001</v>
+        <v>34.4664</v>
       </c>
       <c r="N81">
-        <v>20.93109666666665</v>
+        <v>20.50026666666666</v>
       </c>
       <c r="O81">
-        <v>7.116572866666663</v>
+        <v>6.970090666666666</v>
       </c>
       <c r="P81">
-        <v>13.81452379999999</v>
+        <v>13.530176</v>
       </c>
       <c r="Q81">
-        <v>20.51452379999999</v>
+        <v>20.230176</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3528641416697849</v>
+        <v>0.3667185533119819</v>
       </c>
       <c r="T81">
-        <v>4.002075137528342</v>
+        <v>4.182644565390572</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -8101,7 +8101,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.614977115607779</v>
+        <v>1.594789901662682</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8109,22 +8109,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1208637106623964</v>
+        <v>0.1206999515741379</v>
       </c>
       <c r="C82">
-        <v>148.067361983453</v>
+        <v>144.4330766419912</v>
       </c>
       <c r="D82">
-        <v>527.2273619834531</v>
+        <v>528.3800766419913</v>
       </c>
       <c r="E82">
-        <v>282.0600000000001</v>
+        <v>286.8470000000001</v>
       </c>
       <c r="F82">
-        <v>382.96</v>
+        <v>387.7470000000001</v>
       </c>
       <c r="G82">
         <v>3.8</v>
@@ -8145,28 +8145,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M82">
-        <v>34.4664</v>
+        <v>34.89723000000001</v>
       </c>
       <c r="N82">
-        <v>20.50026666666666</v>
+        <v>20.06943666666665</v>
       </c>
       <c r="O82">
-        <v>6.970090666666666</v>
+        <v>6.823608466666663</v>
       </c>
       <c r="P82">
-        <v>13.530176</v>
+        <v>13.24582819999999</v>
       </c>
       <c r="Q82">
-        <v>20.230176</v>
+        <v>19.94582819999999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3667185533119819</v>
+        <v>0.3820313240744103</v>
       </c>
       <c r="T82">
-        <v>4.182644565390572</v>
+        <v>4.382221301448827</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8183,7 +8183,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.594789901662682</v>
+        <v>1.575101137444624</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8191,22 +8191,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1206999515741379</v>
+        <v>0.1205361924858795</v>
       </c>
       <c r="C83">
-        <v>144.4330766419912</v>
+        <v>140.8038428691264</v>
       </c>
       <c r="D83">
-        <v>528.3800766419913</v>
+        <v>529.5378428691265</v>
       </c>
       <c r="E83">
-        <v>286.8470000000001</v>
+        <v>291.634</v>
       </c>
       <c r="F83">
-        <v>387.7470000000001</v>
+        <v>392.534</v>
       </c>
       <c r="G83">
         <v>3.8</v>
@@ -8227,28 +8227,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M83">
-        <v>34.89723000000001</v>
+        <v>35.32806</v>
       </c>
       <c r="N83">
-        <v>20.06943666666665</v>
+        <v>19.63860666666666</v>
       </c>
       <c r="O83">
-        <v>6.823608466666663</v>
+        <v>6.677126266666665</v>
       </c>
       <c r="P83">
-        <v>13.24582819999999</v>
+        <v>12.9614804</v>
       </c>
       <c r="Q83">
-        <v>19.94582819999999</v>
+        <v>19.6614804</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3820313240744103</v>
+        <v>0.3990455138104417</v>
       </c>
       <c r="T83">
-        <v>4.382221301448827</v>
+        <v>4.603973230402444</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8265,7 +8265,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.575101137444624</v>
+        <v>1.555892586987982</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8273,22 +8273,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1205361924858795</v>
+        <v>0.120372433397621</v>
       </c>
       <c r="C84">
-        <v>140.8038428691264</v>
+        <v>137.1796939441908</v>
       </c>
       <c r="D84">
-        <v>529.5378428691265</v>
+        <v>530.7006939441909</v>
       </c>
       <c r="E84">
-        <v>291.634</v>
+        <v>296.421</v>
       </c>
       <c r="F84">
-        <v>392.534</v>
+        <v>397.3210000000001</v>
       </c>
       <c r="G84">
         <v>3.8</v>
@@ -8309,28 +8309,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M84">
-        <v>35.32806</v>
+        <v>35.75889000000001</v>
       </c>
       <c r="N84">
-        <v>19.63860666666666</v>
+        <v>19.20777666666665</v>
       </c>
       <c r="O84">
-        <v>6.677126266666665</v>
+        <v>6.530644066666663</v>
       </c>
       <c r="P84">
-        <v>12.9614804</v>
+        <v>12.67713259999999</v>
       </c>
       <c r="Q84">
-        <v>19.6614804</v>
+        <v>19.37713259999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3990455138104417</v>
+        <v>0.4180613729271827</v>
       </c>
       <c r="T84">
-        <v>4.603973230402444</v>
+        <v>4.851813621585897</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8347,7 +8347,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.555892586987982</v>
+        <v>1.53714689316885</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8355,22 +8355,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.120372433397621</v>
+        <v>0.1202086743093626</v>
       </c>
       <c r="C85">
-        <v>137.1796939441908</v>
+        <v>133.5606634394823</v>
       </c>
       <c r="D85">
-        <v>530.7006939441909</v>
+        <v>531.8686634394824</v>
       </c>
       <c r="E85">
-        <v>296.421</v>
+        <v>301.2080000000001</v>
       </c>
       <c r="F85">
-        <v>397.3210000000001</v>
+        <v>402.1080000000001</v>
       </c>
       <c r="G85">
         <v>3.8</v>
@@ -8391,28 +8391,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M85">
-        <v>35.75889000000001</v>
+        <v>36.18972</v>
       </c>
       <c r="N85">
-        <v>19.20777666666665</v>
+        <v>18.77694666666666</v>
       </c>
       <c r="O85">
-        <v>6.530644066666663</v>
+        <v>6.384161866666665</v>
       </c>
       <c r="P85">
-        <v>12.67713259999999</v>
+        <v>12.39278479999999</v>
       </c>
       <c r="Q85">
-        <v>19.37713259999999</v>
+        <v>19.0927848</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4180613729271827</v>
+        <v>0.4394542144335165</v>
       </c>
       <c r="T85">
-        <v>4.851813621585897</v>
+        <v>5.130634061667283</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8429,7 +8429,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.53714689316885</v>
+        <v>1.51884752539303</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8437,22 +8437,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1202086743093626</v>
+        <v>0.1200449152211041</v>
       </c>
       <c r="C86">
-        <v>133.5606634394824</v>
+        <v>129.9467852234955</v>
       </c>
       <c r="D86">
-        <v>531.8686634394825</v>
+        <v>533.0417852234956</v>
       </c>
       <c r="E86">
-        <v>301.208</v>
+        <v>305.995</v>
       </c>
       <c r="F86">
-        <v>402.108</v>
+        <v>406.895</v>
       </c>
       <c r="G86">
         <v>3.8</v>
@@ -8473,28 +8473,28 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M86">
-        <v>36.18972</v>
+        <v>36.62055</v>
       </c>
       <c r="N86">
-        <v>18.77694666666666</v>
+        <v>18.34611666666666</v>
       </c>
       <c r="O86">
-        <v>6.384161866666665</v>
+        <v>6.237679666666665</v>
       </c>
       <c r="P86">
-        <v>12.39278479999999</v>
+        <v>12.108437</v>
       </c>
       <c r="Q86">
-        <v>19.0927848</v>
+        <v>18.808437</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4394542144335162</v>
+        <v>0.463699434807361</v>
       </c>
       <c r="T86">
-        <v>5.13063406166728</v>
+        <v>5.446630560426184</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8511,7 +8511,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.51884752539303</v>
+        <v>1.500978730976642</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8519,22 +8519,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1200449152211041</v>
+        <v>0.1583372512193307</v>
       </c>
       <c r="C87">
-        <v>129.9467852234955</v>
+        <v>-56.21495886983189</v>
       </c>
       <c r="D87">
-        <v>533.0417852234956</v>
+        <v>351.6670411301681</v>
       </c>
       <c r="E87">
-        <v>305.995</v>
+        <v>310.782</v>
       </c>
       <c r="F87">
-        <v>406.895</v>
+        <v>411.682</v>
       </c>
       <c r="G87">
         <v>3.8</v>
@@ -8555,45 +8555,45 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M87">
-        <v>36.62055</v>
+        <v>60.43491760000001</v>
       </c>
       <c r="N87">
-        <v>18.34611666666666</v>
+        <v>-5.468250933333344</v>
       </c>
       <c r="O87">
-        <v>6.237679666666665</v>
+        <v>-1.859205317333337</v>
       </c>
       <c r="P87">
-        <v>12.108437</v>
+        <v>-3.609045616000007</v>
       </c>
       <c r="Q87">
-        <v>18.808437</v>
+        <v>3.090954383999996</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.463699434807361</v>
+        <v>0.5080693429430939</v>
       </c>
       <c r="T87">
-        <v>5.446630560426184</v>
+        <v>6.024919204742695</v>
       </c>
       <c r="U87">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.34</v>
+        <v>0.3092362397242131</v>
       </c>
       <c r="W87">
-        <v>0.05939999999999999</v>
+        <v>0.1014041200084855</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y87">
-        <v>1.500978730976642</v>
+        <v>0.9095183521300384</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8601,22 +8601,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1583372512193307</v>
+        <v>0.1593472512193307</v>
       </c>
       <c r="C88">
-        <v>-56.21495886983189</v>
+        <v>-64.13002853005992</v>
       </c>
       <c r="D88">
-        <v>351.6670411301681</v>
+        <v>348.5389714699401</v>
       </c>
       <c r="E88">
-        <v>310.782</v>
+        <v>315.5690000000001</v>
       </c>
       <c r="F88">
-        <v>411.682</v>
+        <v>416.4690000000001</v>
       </c>
       <c r="G88">
         <v>3.8</v>
@@ -8637,37 +8637,37 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M88">
-        <v>60.43491760000001</v>
+        <v>61.13764920000001</v>
       </c>
       <c r="N88">
-        <v>-5.468250933333344</v>
+        <v>-6.170982533333351</v>
       </c>
       <c r="O88">
-        <v>-1.859205317333337</v>
+        <v>-2.09813406133334</v>
       </c>
       <c r="P88">
-        <v>-3.609045616000007</v>
+        <v>-4.072848472000011</v>
       </c>
       <c r="Q88">
-        <v>3.090954383999996</v>
+        <v>2.627151527999992</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5080693429430939</v>
+        <v>0.5436285231694857</v>
       </c>
       <c r="T88">
-        <v>6.024919204742695</v>
+        <v>6.488374528184441</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.3092362397242131</v>
+        <v>0.3056818001871531</v>
       </c>
       <c r="W88">
-        <v>0.1014041200084855</v>
+        <v>0.1019259117325259</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.9095183521300384</v>
+        <v>0.8990641181975092</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8683,22 +8683,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1593472512193307</v>
+        <v>0.1603572512193307</v>
       </c>
       <c r="C89">
-        <v>-64.13002853005992</v>
+        <v>-71.98994061059381</v>
       </c>
       <c r="D89">
-        <v>348.5389714699401</v>
+        <v>345.4660593894062</v>
       </c>
       <c r="E89">
-        <v>315.5690000000001</v>
+        <v>320.356</v>
       </c>
       <c r="F89">
-        <v>416.4690000000001</v>
+        <v>421.256</v>
       </c>
       <c r="G89">
         <v>3.8</v>
@@ -8719,37 +8719,37 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M89">
-        <v>61.13764920000001</v>
+        <v>61.84038080000001</v>
       </c>
       <c r="N89">
-        <v>-6.170982533333351</v>
+        <v>-6.873714133333351</v>
       </c>
       <c r="O89">
-        <v>-2.09813406133334</v>
+        <v>-2.33706280533334</v>
       </c>
       <c r="P89">
-        <v>-4.072848472000011</v>
+        <v>-4.536651328000012</v>
       </c>
       <c r="Q89">
-        <v>2.627151527999992</v>
+        <v>2.163348671999991</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5436285231694857</v>
+        <v>0.5851142334336096</v>
       </c>
       <c r="T89">
-        <v>6.488374528184441</v>
+        <v>7.029072405533145</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.3056818001871531</v>
+        <v>0.3022081433668446</v>
       </c>
       <c r="W89">
-        <v>0.1019259117325259</v>
+        <v>0.1024358445537472</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8990641181975092</v>
+        <v>0.8888474804907193</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8765,22 +8765,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1603572512193307</v>
+        <v>0.1613672512193307</v>
       </c>
       <c r="C90">
-        <v>-71.98994061059381</v>
+        <v>-79.79614126044834</v>
       </c>
       <c r="D90">
-        <v>345.4660593894062</v>
+        <v>342.4468587395517</v>
       </c>
       <c r="E90">
-        <v>320.356</v>
+        <v>325.143</v>
       </c>
       <c r="F90">
-        <v>421.256</v>
+        <v>426.0430000000001</v>
       </c>
       <c r="G90">
         <v>3.8</v>
@@ -8801,37 +8801,37 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M90">
-        <v>61.84038080000001</v>
+        <v>62.54311240000001</v>
       </c>
       <c r="N90">
-        <v>-6.873714133333351</v>
+        <v>-7.576445733333351</v>
       </c>
       <c r="O90">
-        <v>-2.33706280533334</v>
+        <v>-2.575991549333339</v>
       </c>
       <c r="P90">
-        <v>-4.536651328000012</v>
+        <v>-5.000454184000011</v>
       </c>
       <c r="Q90">
-        <v>2.163348671999991</v>
+        <v>1.699545815999992</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5851142334336096</v>
+        <v>0.6341428001093923</v>
       </c>
       <c r="T90">
-        <v>7.029072405533145</v>
+        <v>7.668078987854341</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.3022081433668446</v>
+        <v>0.2988125462503631</v>
       </c>
       <c r="W90">
-        <v>0.1024358445537472</v>
+        <v>0.1029343182104467</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8888474804907193</v>
+        <v>0.8788604301481269</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8847,22 +8847,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1613672512193307</v>
+        <v>0.1623772512193307</v>
       </c>
       <c r="C91">
-        <v>-79.79614126044834</v>
+        <v>-87.55002651215341</v>
       </c>
       <c r="D91">
-        <v>342.4468587395517</v>
+        <v>339.4799734878466</v>
       </c>
       <c r="E91">
-        <v>325.143</v>
+        <v>329.9300000000001</v>
       </c>
       <c r="F91">
-        <v>426.0430000000001</v>
+        <v>430.83</v>
       </c>
       <c r="G91">
         <v>3.8</v>
@@ -8883,37 +8883,37 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M91">
-        <v>62.54311240000001</v>
+        <v>63.24584400000001</v>
       </c>
       <c r="N91">
-        <v>-7.576445733333351</v>
+        <v>-8.279177333333351</v>
       </c>
       <c r="O91">
-        <v>-2.575991549333339</v>
+        <v>-2.81492029333334</v>
       </c>
       <c r="P91">
-        <v>-5.000454184000011</v>
+        <v>-5.464257040000011</v>
       </c>
       <c r="Q91">
-        <v>1.699545815999992</v>
+        <v>1.235742959999992</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6341428001093923</v>
+        <v>0.6929770801203315</v>
       </c>
       <c r="T91">
-        <v>7.668078987854341</v>
+        <v>8.434886886639775</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.2988125462503631</v>
+        <v>0.2954924068475814</v>
       </c>
       <c r="W91">
-        <v>0.1029343182104467</v>
+        <v>0.1034217146747751</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8788604301481269</v>
+        <v>0.8690953142575921</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8929,22 +8929,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1623772512193307</v>
+        <v>0.1633872512193307</v>
       </c>
       <c r="C92">
-        <v>-87.55002651215341</v>
+        <v>-95.25294443409859</v>
       </c>
       <c r="D92">
-        <v>339.4799734878466</v>
+        <v>336.5640555659015</v>
       </c>
       <c r="E92">
-        <v>329.9300000000001</v>
+        <v>334.7170000000001</v>
       </c>
       <c r="F92">
-        <v>430.83</v>
+        <v>435.6170000000001</v>
       </c>
       <c r="G92">
         <v>3.8</v>
@@ -8965,37 +8965,37 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M92">
-        <v>63.24584400000001</v>
+        <v>63.94857560000002</v>
       </c>
       <c r="N92">
-        <v>-8.279177333333351</v>
+        <v>-8.981908933333358</v>
       </c>
       <c r="O92">
-        <v>-2.81492029333334</v>
+        <v>-3.053849037333342</v>
       </c>
       <c r="P92">
-        <v>-5.464257040000011</v>
+        <v>-5.928059896000017</v>
       </c>
       <c r="Q92">
-        <v>1.235742959999992</v>
+        <v>0.7719401039999862</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6929770801203315</v>
+        <v>0.7648856445781462</v>
       </c>
       <c r="T92">
-        <v>8.434886886639775</v>
+        <v>9.372096540710862</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.2954924068475814</v>
+        <v>0.292245237541564</v>
       </c>
       <c r="W92">
-        <v>0.1034217146747751</v>
+        <v>0.1038983991288984</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8690953142575921</v>
+        <v>0.8595448162987175</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9011,22 +9011,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1633872512193307</v>
+        <v>0.1643972512193307</v>
       </c>
       <c r="C93">
-        <v>-95.25294443409859</v>
+        <v>-102.9061971728988</v>
       </c>
       <c r="D93">
-        <v>336.5640555659015</v>
+        <v>333.6978028271013</v>
       </c>
       <c r="E93">
-        <v>334.7170000000001</v>
+        <v>339.504</v>
       </c>
       <c r="F93">
-        <v>435.6170000000001</v>
+        <v>440.4040000000001</v>
       </c>
       <c r="G93">
         <v>3.8</v>
@@ -9047,37 +9047,37 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M93">
-        <v>63.94857560000002</v>
+        <v>64.65130720000002</v>
       </c>
       <c r="N93">
-        <v>-8.981908933333358</v>
+        <v>-9.684640533333358</v>
       </c>
       <c r="O93">
-        <v>-3.053849037333342</v>
+        <v>-3.292777781333342</v>
       </c>
       <c r="P93">
-        <v>-5.928059896000017</v>
+        <v>-6.391862752000016</v>
       </c>
       <c r="Q93">
-        <v>0.7719401039999862</v>
+        <v>0.3081372479999871</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7648856445781462</v>
+        <v>0.8547713501504148</v>
       </c>
       <c r="T93">
-        <v>9.372096540710862</v>
+        <v>10.54360860829972</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.292245237541564</v>
+        <v>0.2890686588726339</v>
       </c>
       <c r="W93">
-        <v>0.1038983991288984</v>
+        <v>0.1043647208774974</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8595448162987175</v>
+        <v>0.8502019378606879</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9093,22 +9093,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1643972512193307</v>
+        <v>0.1654072512193307</v>
       </c>
       <c r="C94">
-        <v>-102.9061971728988</v>
+        <v>-110.5110428922801</v>
       </c>
       <c r="D94">
-        <v>333.6978028271013</v>
+        <v>330.87995710772</v>
       </c>
       <c r="E94">
-        <v>339.504</v>
+        <v>344.2910000000001</v>
       </c>
       <c r="F94">
-        <v>440.4040000000001</v>
+        <v>445.1910000000001</v>
       </c>
       <c r="G94">
         <v>3.8</v>
@@ -9129,37 +9129,37 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M94">
-        <v>64.65130720000002</v>
+        <v>65.35403880000001</v>
       </c>
       <c r="N94">
-        <v>-9.684640533333358</v>
+        <v>-10.38737213333335</v>
       </c>
       <c r="O94">
-        <v>-3.292777781333342</v>
+        <v>-3.531706525333339</v>
       </c>
       <c r="P94">
-        <v>-6.391862752000016</v>
+        <v>-6.855665608000011</v>
       </c>
       <c r="Q94">
-        <v>0.3081372479999871</v>
+        <v>-0.1556656080000085</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8547713501504148</v>
+        <v>0.9703386858861883</v>
       </c>
       <c r="T94">
-        <v>10.54360860829972</v>
+        <v>12.0498384094854</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.2890686588726339</v>
+        <v>0.2859603937234658</v>
       </c>
       <c r="W94">
-        <v>0.1043647208774974</v>
+        <v>0.1048210142013952</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8502019378606879</v>
+        <v>0.8410599815396054</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9175,22 +9175,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1654072512193307</v>
+        <v>0.1664172512193307</v>
       </c>
       <c r="C95">
-        <v>-110.5110428922801</v>
+        <v>-118.0686976145561</v>
       </c>
       <c r="D95">
-        <v>330.87995710772</v>
+        <v>328.1093023854439</v>
       </c>
       <c r="E95">
-        <v>344.2910000000001</v>
+        <v>349.0780000000001</v>
       </c>
       <c r="F95">
-        <v>445.1910000000001</v>
+        <v>449.9780000000001</v>
       </c>
       <c r="G95">
         <v>3.8</v>
@@ -9211,37 +9211,37 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M95">
-        <v>65.35403880000001</v>
+        <v>66.05677040000002</v>
       </c>
       <c r="N95">
-        <v>-10.38737213333335</v>
+        <v>-11.09010373333336</v>
       </c>
       <c r="O95">
-        <v>-3.531706525333339</v>
+        <v>-3.770635269333342</v>
       </c>
       <c r="P95">
-        <v>-6.855665608000011</v>
+        <v>-7.319468464000016</v>
       </c>
       <c r="Q95">
-        <v>-0.1556656080000085</v>
+        <v>-0.619468464000013</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9703386858861883</v>
+        <v>1.12442846686722</v>
       </c>
       <c r="T95">
-        <v>12.0498384094854</v>
+        <v>14.0581448110663</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.2859603937234658</v>
+        <v>0.2829182618753439</v>
       </c>
       <c r="W95">
-        <v>0.1048210142013952</v>
+        <v>0.1052675991566995</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8410599815396054</v>
+        <v>0.8321125349274818</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9257,22 +9257,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1664172512193307</v>
+        <v>0.1674272512193307</v>
       </c>
       <c r="C96">
-        <v>-118.0686976145561</v>
+        <v>-125.5803369703509</v>
       </c>
       <c r="D96">
-        <v>328.1093023854439</v>
+        <v>325.3846630296492</v>
       </c>
       <c r="E96">
-        <v>349.0780000000001</v>
+        <v>353.8650000000001</v>
       </c>
       <c r="F96">
-        <v>449.9780000000001</v>
+        <v>454.7650000000001</v>
       </c>
       <c r="G96">
         <v>3.8</v>
@@ -9293,37 +9293,37 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M96">
-        <v>66.05677040000002</v>
+        <v>66.75950200000003</v>
       </c>
       <c r="N96">
-        <v>-11.09010373333336</v>
+        <v>-11.79283533333336</v>
       </c>
       <c r="O96">
-        <v>-3.770635269333342</v>
+        <v>-4.009564013333344</v>
       </c>
       <c r="P96">
-        <v>-7.319468464000016</v>
+        <v>-7.78327132000002</v>
       </c>
       <c r="Q96">
-        <v>-0.619468464000013</v>
+        <v>-1.083271320000017</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.12442846686722</v>
+        <v>1.340154160240665</v>
       </c>
       <c r="T96">
-        <v>14.0581448110663</v>
+        <v>16.86977377327957</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.2829182618753439</v>
+        <v>0.2799401749082349</v>
       </c>
       <c r="W96">
-        <v>0.1052675991566995</v>
+        <v>0.1057047823234711</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8321125349274818</v>
+        <v>0.8233534556124555</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9339,22 +9339,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1674272512193307</v>
+        <v>0.1684372512193307</v>
       </c>
       <c r="C97">
-        <v>-125.5803369703509</v>
+        <v>-133.0470978618615</v>
       </c>
       <c r="D97">
-        <v>325.3846630296492</v>
+        <v>322.7049021381386</v>
       </c>
       <c r="E97">
-        <v>353.8650000000001</v>
+        <v>358.652</v>
       </c>
       <c r="F97">
-        <v>454.7650000000001</v>
+        <v>459.5520000000001</v>
       </c>
       <c r="G97">
         <v>3.8</v>
@@ -9375,37 +9375,37 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M97">
-        <v>66.75950200000003</v>
+        <v>67.46223360000002</v>
       </c>
       <c r="N97">
-        <v>-11.79283533333336</v>
+        <v>-12.49556693333336</v>
       </c>
       <c r="O97">
-        <v>-4.009564013333344</v>
+        <v>-4.248492757333342</v>
       </c>
       <c r="P97">
-        <v>-7.78327132000002</v>
+        <v>-8.247074176000016</v>
       </c>
       <c r="Q97">
-        <v>-1.083271320000017</v>
+        <v>-1.547074176000013</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.340154160240665</v>
+        <v>1.663742700300832</v>
       </c>
       <c r="T97">
-        <v>16.86977377327957</v>
+        <v>21.08721721659947</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.2799401749082349</v>
+        <v>0.2770241314196075</v>
       </c>
       <c r="W97">
-        <v>0.1057047823234711</v>
+        <v>0.1061328575076016</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8233534556124555</v>
+        <v>0.8147768571164926</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9421,22 +9421,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1684372512193307</v>
+        <v>0.1694472512193307</v>
       </c>
       <c r="C98">
-        <v>-133.0470978618615</v>
+        <v>-140.4700800446062</v>
       </c>
       <c r="D98">
-        <v>322.7049021381386</v>
+        <v>320.0689199553939</v>
       </c>
       <c r="E98">
-        <v>358.652</v>
+        <v>363.4390000000001</v>
       </c>
       <c r="F98">
-        <v>459.552</v>
+        <v>464.3390000000001</v>
       </c>
       <c r="G98">
         <v>3.8</v>
@@ -9457,37 +9457,37 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M98">
-        <v>67.4622336</v>
+        <v>68.16496520000001</v>
       </c>
       <c r="N98">
-        <v>-12.49556693333334</v>
+        <v>-13.19829853333335</v>
       </c>
       <c r="O98">
-        <v>-4.248492757333337</v>
+        <v>-4.48742150133334</v>
       </c>
       <c r="P98">
-        <v>-8.247074176000005</v>
+        <v>-8.71087703200001</v>
       </c>
       <c r="Q98">
-        <v>-1.547074176000002</v>
+        <v>-2.010877032000007</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.663742700300827</v>
+        <v>2.203056933734437</v>
       </c>
       <c r="T98">
-        <v>21.08721721659942</v>
+        <v>28.11628962213256</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.2770241314196075</v>
+        <v>0.274168212538993</v>
       </c>
       <c r="W98">
-        <v>0.1061328575076016</v>
+        <v>0.1065521063992758</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8147768571164928</v>
+        <v>0.8063770957029206</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9503,22 +9503,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1694472512193307</v>
+        <v>0.2296826466595503</v>
       </c>
       <c r="C99">
-        <v>-140.4700800446062</v>
+        <v>-250.1037217036864</v>
       </c>
       <c r="D99">
-        <v>320.0689199553939</v>
+        <v>215.2222782963136</v>
       </c>
       <c r="E99">
-        <v>363.4390000000001</v>
+        <v>368.226</v>
       </c>
       <c r="F99">
-        <v>464.3390000000001</v>
+        <v>469.126</v>
       </c>
       <c r="G99">
         <v>3.8</v>
@@ -9539,45 +9539,45 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M99">
-        <v>68.16496520000001</v>
+        <v>94.20050080000001</v>
       </c>
       <c r="N99">
-        <v>-13.19829853333335</v>
+        <v>-39.23383413333335</v>
       </c>
       <c r="O99">
-        <v>-4.48742150133334</v>
+        <v>-13.33950360533334</v>
       </c>
       <c r="P99">
-        <v>-8.71087703200001</v>
+        <v>-25.89433052800001</v>
       </c>
       <c r="Q99">
-        <v>-2.010877032000007</v>
+        <v>-19.19433052800001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.203056933734437</v>
+        <v>3.596955172612634</v>
       </c>
       <c r="T99">
-        <v>28.11628962213256</v>
+        <v>46.28345644181953</v>
       </c>
       <c r="U99">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.274168212538993</v>
+        <v>0.1983924343071716</v>
       </c>
       <c r="W99">
-        <v>0.1065521063992758</v>
+        <v>0.1609627991911199</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y99">
-        <v>0.8063770957029206</v>
+        <v>0.5835071597269752</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9585,22 +9585,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2296826466595503</v>
+        <v>0.2312326466595503</v>
       </c>
       <c r="C100">
-        <v>-250.1037217036864</v>
+        <v>-256.68972817514</v>
       </c>
       <c r="D100">
-        <v>215.2222782963136</v>
+        <v>213.42327182486</v>
       </c>
       <c r="E100">
-        <v>368.226</v>
+        <v>373.013</v>
       </c>
       <c r="F100">
-        <v>469.126</v>
+        <v>473.9130000000001</v>
       </c>
       <c r="G100">
         <v>3.8</v>
@@ -9621,37 +9621,37 @@
         <v>54.96666666666666</v>
       </c>
       <c r="M100">
-        <v>94.20050080000001</v>
+        <v>95.16173040000001</v>
       </c>
       <c r="N100">
-        <v>-39.23383413333335</v>
+        <v>-40.19506373333335</v>
       </c>
       <c r="O100">
-        <v>-13.33950360533334</v>
+        <v>-13.66632166933334</v>
       </c>
       <c r="P100">
-        <v>-25.89433052800001</v>
+        <v>-26.52874206400001</v>
       </c>
       <c r="Q100">
-        <v>-19.19433052800001</v>
+        <v>-19.82874206400001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.596955172612634</v>
+        <v>7.148110345225269</v>
       </c>
       <c r="T100">
-        <v>46.28345644181953</v>
+        <v>92.56691288363906</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1983924343071716</v>
+        <v>0.1963884703242709</v>
       </c>
       <c r="W100">
-        <v>0.1609627991911199</v>
+        <v>0.1613651951588864</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9659,91 +9659,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5835071597269752</v>
+        <v>0.5776131480125613</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2312326466595503</v>
-      </c>
-      <c r="C101">
-        <v>-256.68972817514</v>
-      </c>
-      <c r="D101">
-        <v>213.42327182486</v>
-      </c>
-      <c r="E101">
-        <v>373.013</v>
-      </c>
-      <c r="F101">
-        <v>473.9130000000001</v>
-      </c>
-      <c r="G101">
-        <v>3.8</v>
-      </c>
-      <c r="H101">
-        <v>377.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>61.66666666666666</v>
-      </c>
-      <c r="K101">
-        <v>6.700000000000003</v>
-      </c>
-      <c r="L101">
-        <v>54.96666666666666</v>
-      </c>
-      <c r="M101">
-        <v>95.16173040000001</v>
-      </c>
-      <c r="N101">
-        <v>-40.19506373333335</v>
-      </c>
-      <c r="O101">
-        <v>-13.66632166933334</v>
-      </c>
-      <c r="P101">
-        <v>-26.52874206400001</v>
-      </c>
-      <c r="Q101">
-        <v>-19.82874206400001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.148110345225269</v>
-      </c>
-      <c r="T101">
-        <v>92.56691288363906</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1963884703242709</v>
-      </c>
-      <c r="W101">
-        <v>0.1613651951588864</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5776131480125613</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
